--- a/files/thebookman-booklist.xlsx
+++ b/files/thebookman-booklist.xlsx
@@ -535,54 +535,54 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>여름</t>
+          <t>품격 있는 대화를 위한 지식 브리핑 (10만 부 기념 특별 한정판)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>이디스 워튼 (지은이), 민지현 (옮긴이)</t>
+          <t>김진 (지은이)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>머묾</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>19000</v>
+        <v>25000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9791124038802</t>
+          <t>9791124038413</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401985055</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=404263026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>위대한 개츠비</t>
+          <t>여름</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>프랜시스 스콧 피츠제럴드 (지은이), 이미정 (옮긴이)</t>
+          <t>이디스 워튼 (지은이), 민지현 (옮긴이)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -605,25 +605,25 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9791124038659</t>
+          <t>9791124038802</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401984756</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401985055</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파리는 언제나 축제</t>
+          <t>위대한 개츠비</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>어니스트 헤밍웨이 (지은이), 권진아 (옮긴이)</t>
+          <t>프랜시스 스콧 피츠제럴드 (지은이), 이미정 (옮긴이)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -646,39 +646,35 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9791124038666</t>
+          <t>9791124038659</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401985497</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401984756</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>단단히, 휩쓸리지 않고 살아간다는 것</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>흔들리는 시간을 지혜롭게 건너는 마음의 철학</t>
-        </is>
-      </c>
+          <t>파리는 언제나 축제</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>나디 미리안 (지은이), 김지유 (옮긴이)</t>
+          <t>어니스트 헤밍웨이 (지은이), 권진아 (옮긴이)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>머묾</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -687,88 +683,88 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9791124038888</t>
+          <t>9791124038666</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=403488397</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401985497</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>머니 트렌드 2027</t>
+          <t>단단히, 휩쓸리지 않고 살아간다는 것</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>격변의 위기를 기회로 바꾸는 55가지 돈의 흐름</t>
+          <t>흔들리는 시간을 지혜롭게 건너는 마음의 철학</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>정태익, 김도윤, 김광석, 김용섭, 김학렬, 박세익, 박정호, 이효석 (지은이)</t>
+          <t>나디 미리안 (지은이), 김지유 (옮긴이)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>27500</v>
+        <v>22000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9791124038826</t>
+          <t>9791124038888</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401122536</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=403488397</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>처음 만나는 철학의 세계</t>
+          <t>머니 트렌드 2027</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>삶에 철학이 들어오는 순간</t>
+          <t>격변의 위기를 기회로 바꾸는 55가지 돈의 흐름</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>성창원 (지은이)</t>
+          <t>정태익, 김도윤, 김광석, 김용섭, 김학렬, 박세익, 박정호, 이효석 (지은이)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -777,33 +773,33 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>22000</v>
+        <v>27500</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9791124038833</t>
+          <t>9791124038826</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=402017704</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401122536</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>똑똑한 사람은 어떻게 말하는가</t>
+          <t>처음 만나는 철학의 세계</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>길게 말하지 않아도 신뢰받는 사람들의 말하기 전략</t>
+          <t>삶에 철학이 들어오는 순간</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>이시한 (지은이)</t>
+          <t>성창원 (지은이)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -813,12 +809,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -826,171 +822,175 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9791124038642</t>
+          <t>9791124038833</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=400007561</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=402017704</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>기억의 무늬</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>똑똑한 사람은 어떻게 말하는가</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>길게 말하지 않아도 신뢰받는 사람들의 말하기 전략</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>백희성 (지은이)</t>
+          <t>이시한 (지은이)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>19800</v>
+        <v>22000</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9791124038604</t>
+          <t>9791124038642</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=398993923</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=400007561</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>나는 도대체 왜 눈치를 볼까</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>타인의 기대에서 벗어나 원하는 삶을 사는 법</t>
-        </is>
-      </c>
+          <t>기억의 무늬</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>케리 올리치, 켈리 권터 (지은이), 김잔디 (옮긴이)</t>
+          <t>백희성 (지은이)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>21000</v>
+        <v>19800</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9791124038536</t>
+          <t>9791124038604</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=397995935</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=398993923</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>만일 나에게 단 한 번의 아침이 남아 있다면 (굿모닝 에디션)</t>
+          <t>나는 도대체 왜 눈치를 볼까</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>오늘이 끝나기 전 반드시 깨달아야 할 것들</t>
+          <t>타인의 기대에서 벗어나 원하는 삶을 사는 법</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>존 릴런드 (지은이), 최인하 (옮긴이)</t>
+          <t>케리 올리치, 켈리 권터 (지은이), 김잔디 (옮긴이)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>19800</v>
+        <v>21000</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9791193937112</t>
+          <t>9791124038536</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=398820063</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=397995935</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>너의 행복은 나의 기쁨이야</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>만일 나에게 단 한 번의 아침이 남아 있다면 (굿모닝 에디션)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>오늘이 끝나기 전 반드시 깨달아야 할 것들</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>정한경 (지은이)</t>
+          <t>존 릴런드 (지은이), 최인하 (옮긴이)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -998,80 +998,76 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9791124038574</t>
+          <t>9791193937112</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396794390</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=398820063</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>여름 (썸머 에디션)</t>
+          <t>너의 행복은 나의 기쁨이야</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>이디스 워튼 (지은이), 민지현 (옮긴이)</t>
+          <t>정한경 (지은이)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>머묾</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>19000</v>
+        <v>19800</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9791124038581</t>
+          <t>9791124038574</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396568091</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396794390</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>끌리는 사람의 비밀</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>마음을 움직이는 품위 있는 말과 태도</t>
-        </is>
-      </c>
+          <t>여름 (썸머 에디션)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>조수빈 (지은이)</t>
+          <t>이디스 워튼 (지은이), 민지현 (옮긴이)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>머묾</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1080,38 +1076,38 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9791124038567</t>
+          <t>9791124038581</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396156367</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396568091</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>최소한의 습관</t>
+          <t>끌리는 사람의 비밀</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>작은 시작으로 압도적 변화를 만드는 행동 공식</t>
+          <t>마음을 움직이는 품위 있는 말과 태도</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>로버트 마우어 (지은이), 장원철 (옮긴이)</t>
+          <t>조수빈 (지은이)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1121,74 +1117,78 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>19800</v>
+        <v>22000</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9791124038512</t>
+          <t>9791124038567</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=394919714</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396156367</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>이방인</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>최소한의 습관</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>작은 시작으로 압도적 변화를 만드는 행동 공식</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>알베르 카뮈 (지은이), 한수민 (옮긴이)</t>
+          <t>로버트 마우어 (지은이), 장원철 (옮긴이)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>머묾</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>18000</v>
+        <v>19800</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9791124038390</t>
+          <t>9791124038512</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396164215</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=394919714</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>프랑켄슈타인</t>
+          <t>이방인</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>메리 셸리 (지은이), 이미애 (옮긴이)</t>
+          <t>알베르 카뮈 (지은이), 한수민 (옮긴이)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1207,29 +1207,29 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>21000</v>
+        <v>18000</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9791124038383</t>
+          <t>9791124038390</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396166191</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396164215</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>올랜도</t>
+          <t>프랑켄슈타인</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>버지니아 울프 (지은이), 정해영 (옮긴이)</t>
+          <t>메리 셸리 (지은이), 이미애 (옮긴이)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1248,34 +1248,34 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>20000</v>
+        <v>21000</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9791124038406</t>
+          <t>9791124038383</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396167382</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396166191</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>리치먼드힐의 이층 버스</t>
+          <t>올랜도</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>이경진 (지은이)</t>
+          <t>버지니아 울프 (지은이), 정해영 (옮긴이)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>머묾</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1289,188 +1289,188 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9791124038499</t>
+          <t>9791124038406</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=394084608</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396167382</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>밤의 설계자</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>잠들기 전 15분, 미래를 바꾸는 밤 생각 습관</t>
-        </is>
-      </c>
+          <t>리치먼드힐의 이층 버스</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>폴커 부슈 (지은이), 이상희 (옮긴이)</t>
+          <t>이경진 (지은이)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>9791124038468</t>
+          <t>9791124038499</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=393318252</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=394084608</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>웨딩 피플</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>밤의 설계자</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>잠들기 전 15분, 미래를 바꾸는 밤 생각 습관</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>앨리슨 에스파흐 (지은이), 김보람 (옮긴이)</t>
+          <t>폴커 부슈 (지은이), 이상희 (옮긴이)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>9791124038437</t>
+          <t>9791124038468</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=392621945</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=393318252</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>아우슈비츠의 무용수</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>인생은 언제나 다시 선택할 수 있다</t>
-        </is>
-      </c>
+          <t>웨딩 피플</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>에디트 에바 에거 (지은이), 안진희 (옮긴이)</t>
+          <t>앨리슨 에스파흐 (지은이), 김보람 (옮긴이)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>24000</v>
+        <v>21000</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>9791124038352</t>
+          <t>9791124038437</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=391538652</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=392621945</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>품격 있는 대화를 위한 지식 브리핑 (10만 부 기념 특별 한정판)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>아우슈비츠의 무용수</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>인생은 언제나 다시 선택할 수 있다</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>김진 (지은이)</t>
+          <t>에디트 에바 에거 (지은이), 안진희 (옮긴이)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>25000</v>
+        <v>24000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>9791124038413</t>
+          <t>9791124038352</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=404263026</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=391538652</t>
         </is>
       </c>
     </row>
@@ -5723,37 +5723,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Money Trend 2027</t>
+          <t>A Briefing on Knowledge for Conversations Worth Having (Special Limited Edition)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55 currents of money that turn upheaval into opportunity.</t>
+          <t>The knowledge behind thoughtful, well-informed conversation.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>머니 트렌드 2027</t>
+          <t>품격 있는 대화를 위한 지식 브리핑 (10만 부 기념 특별 한정판)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>정태익, 김도윤, 김광석, 김용섭, 김학렬, 박세익, 박정호, 이효석</t>
+          <t>김진</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>9791124038826</t>
+          <t>9791124038413</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5765,27 +5765,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Meeting Philosophy for the First Time</t>
+          <t>Money Trend 2027</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The moment philosophy walks into your life.</t>
+          <t>55 currents of money that turn upheaval into opportunity.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>처음 만나는 철학의 세계</t>
+          <t>머니 트렌드 2027</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>성창원</t>
+          <t>정태익, 김도윤, 김광석, 김용섭, 김학렬, 박세익, 박정호, 이효석</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9791124038833</t>
+          <t>9791124038826</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5807,37 +5807,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>How Smart People Talk</t>
+          <t>Meeting Philosophy for the First Time</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Speaking strategies of people who earn trust without talking long.</t>
+          <t>The moment philosophy walks into your life.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>똑똑한 사람은 어떻게 말하는가</t>
+          <t>처음 만나는 철학의 세계</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>이시한</t>
+          <t>성창원</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9791124038642</t>
+          <t>9791124038833</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5849,37 +5849,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>The Texture of Memory</t>
+          <t>How Smart People Talk</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unable to recognize faces, she reads people through cloth and gait.</t>
+          <t>Speaking strategies of people who earn trust without talking long.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>기억의 무늬</t>
+          <t>똑똑한 사람은 어떻게 말하는가</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>백희성</t>
+          <t>이시한</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9791124038604</t>
+          <t>9791124038642</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5891,37 +5891,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Your Happiness Is My Joy</t>
+          <t>The Texture of Memory</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>To love someone is to find your joy in theirs.</t>
+          <t>Unable to recognize faces, she reads people through cloth and gait.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>너의 행복은 나의 기쁨이야</t>
+          <t>기억의 무늬</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>정한경</t>
+          <t>백희성</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9791124038574</t>
+          <t>9791124038604</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5933,37 +5933,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>The Secret of Magnetic People</t>
+          <t>Your Happiness Is My Joy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Graceful words and bearing that move hearts.</t>
+          <t>To love someone is to find your joy in theirs.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>끌리는 사람의 비밀</t>
+          <t>너의 행복은 나의 기쁨이야</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>조수빈</t>
+          <t>정한경</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>9791124038567</t>
+          <t>9791124038574</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -5975,37 +5975,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>The Double-Decker Bus of Richmond Hill</t>
+          <t>The Secret of Magnetic People</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>If you could change the past, would you choose differently?</t>
+          <t>Graceful words and bearing that move hearts.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>리치먼드힐의 이층 버스</t>
+          <t>끌리는 사람의 비밀</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>이경진</t>
+          <t>조수빈</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9791124038499</t>
+          <t>9791124038567</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -6017,37 +6017,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A Briefing on Knowledge for Conversations Worth Having (Special Limited Edition)</t>
+          <t>The Double-Decker Bus of Richmond Hill</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The knowledge behind thoughtful, well-informed conversation.</t>
+          <t>If you could change the past, would you choose differently?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>품격 있는 대화를 위한 지식 브리핑 (10만 부 기념 특별 한정판)</t>
+          <t>리치먼드힐의 이층 버스</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>김진</t>
+          <t>이경진</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9791124038413</t>
+          <t>9791124038499</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">

--- a/files/thebookman-booklist.xlsx
+++ b/files/thebookman-booklist.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3676,72 +3676,72 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>새들이 남쪽으로 가는 날</t>
+          <t>왜 그들만 부자가 되는가</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024 스웨덴 올해의 도서상 수상작</t>
+          <t>부의 격차를 좁히는 진짜 돈의 모습</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>리사 리드센 (지은이), 손화수 (옮긴이)</t>
+          <t>필립 바구스, 안드레아스 마르크바르트 (지은이), 배진아 (옮긴이)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>19500</v>
+        <v>22000</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>9791193937372</t>
+          <t>9791193937396</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=352764746</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=354574933</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>삶의 태도</t>
+          <t>새들이 남쪽으로 가는 날</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>흔들림 없이 나아가는</t>
+          <t>2024 스웨덴 올해의 도서상 수상작</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>반건호 (지은이)</t>
+          <t>리사 리드센 (지은이), 손화수 (옮긴이)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3750,213 +3750,213 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>22000</v>
+        <v>19500</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>9791193937402</t>
+          <t>9791193937372</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=353472576</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=352764746</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>인생을 자유롭게 하는 것들</t>
+          <t>삶의 태도</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>가슴 뛰는 삶을 향해 가는 최우선의 행복</t>
+          <t>흔들림 없이 나아가는</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>나용민, 유숙현 (지은이)</t>
+          <t>반건호 (지은이)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>18000</v>
+        <v>22000</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>9791193937389</t>
+          <t>9791193937402</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=353117247</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=353472576</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>쉼과 나아감에 대하여</t>
+          <t>인생을 자유롭게 하는 것들</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>인생의 오아시스를 만나는 예일대 명강의</t>
+          <t>가슴 뛰는 삶을 향해 가는 최우선의 행복</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>마릴린 폴 (지은이), 김태훈 (옮긴이)</t>
+          <t>나용민, 유숙현 (지은이)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>19800</v>
+        <v>18000</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>9791193937341</t>
+          <t>9791193937389</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=351959853</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=353117247</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>영국 아빠 피터의 하루 3분 영어 대화 (스프링)</t>
+          <t>쉼과 나아감에 대하여</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>스스로 말하고 표현하는 영어 회화 일력</t>
+          <t>인생의 오아시스를 만나는 예일대 명강의</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>피터 빈트 (지은이)</t>
+          <t>마릴린 폴 (지은이), 김태훈 (옮긴이)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>북크레용</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>자녀교육</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>25000</v>
+        <v>19800</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>9791193937280</t>
+          <t>9791193937341</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=350405920</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=351959853</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>질투라는 감옥</t>
+          <t>영국 아빠 피터의 하루 3분 영어 대화 (스프링)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>우리는 왜 타인에게 휘둘리는가</t>
+          <t>스스로 말하고 표현하는 영어 회화 일력</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>야마모토 케이 (지은이), 최주연 (옮긴이)</t>
+          <t>피터 빈트 (지은이)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북크레용</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>자녀교육</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>19800</v>
+        <v>25000</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>9791193937259</t>
+          <t>9791193937280</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=348985847</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=350405920</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>머니 트렌드 2025</t>
+          <t>질투라는 감옥</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>새로운 부의 기회를 선점할 55가지 성공 시나리오</t>
+          <t>우리는 왜 타인에게 휘둘리는가</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>정태익, 김도윤, 김광석, 김용섭, 김현준, 정수종, 채상욱, 최재붕 (지은이)</t>
+          <t>야마모토 케이 (지은이), 최주연 (옮긴이)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3966,143 +3966,147 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>25000</v>
+        <v>19800</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>9791193937211</t>
+          <t>9791193937259</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=345965820</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=348985847</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>마음이 부자인 아이는 어떻게 성장하는가</t>
+          <t>머니 트렌드 2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>행복할 줄 아는 아이로 키우는 정서 육아법</t>
+          <t>새로운 부의 기회를 선점할 55가지 성공 시나리오</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>박소영 (지은이)</t>
+          <t>정태익, 김도윤, 김광석, 김용섭, 김현준, 정수종, 채상욱, 최재붕 (지은이)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>북크레용</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>자녀교육</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>19800</v>
+        <v>25000</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>9791193937228</t>
+          <t>9791193937211</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=346892914</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=345965820</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>엄마에게 안부를 묻는 밤</t>
+          <t>마음이 부자인 아이는 어떻게 성장하는가</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>언제나 내 편인 이 세상 단 한 사람</t>
+          <t>행복할 줄 아는 아이로 키우는 정서 육아법</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>박애희 (지은이)</t>
+          <t>박소영 (지은이)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북크레용</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자녀교육</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>18800</v>
+        <v>19800</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>9791193937242</t>
+          <t>9791193937228</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=346467345</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=346892914</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>빛이 이끄는 곳으로</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>엄마에게 안부를 묻는 밤</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>언제나 내 편인 이 세상 단 한 사람</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>백희성 (지은이)</t>
+          <t>박애희 (지은이)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -4110,29 +4114,25 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>9791193937198</t>
+          <t>9791193937242</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=344497704</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=346467345</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>호감의 시작 (트윙클 에디션)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>관계, 일, 인생이 풀리는 매력의 법칙</t>
-        </is>
-      </c>
+          <t>빛이 이끄는 곳으로</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>희렌최 (지은이)</t>
+          <t>백희성 (지은이)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4142,47 +4142,47 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>18500</v>
+        <v>18800</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>9791193937143</t>
+          <t>9791193937198</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=342932323</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=344497704</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>나는 도대체 왜 피곤할까</t>
+          <t>호감의 시작 (트윙클 에디션)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>이 죽일 놈의 피로와 결별하는 법</t>
+          <t>관계, 일, 인생이 풀리는 매력의 법칙</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>에이미 샤 (지은이), 김잔디 (옮긴이)</t>
+          <t>희렌최 (지은이)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4192,33 +4192,37 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>19800</v>
+        <v>18500</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>9791193937136</t>
+          <t>9791193937143</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=342083093</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=342932323</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>그럼에도 불구하고 나는 내가 좋았어</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>나는 도대체 왜 피곤할까</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>이 죽일 놈의 피로와 결별하는 법</t>
+        </is>
+      </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>박채린 (지은이)</t>
+          <t>에이미 샤 (지은이), 김잔디 (옮긴이)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4228,102 +4232,98 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>18000</v>
+        <v>19800</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>9791193937105</t>
+          <t>9791193937136</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=340511549</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=342083093</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>부자의 마지막 가르침 (30만 부 리커버)</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>삶의 자유를 위한 부의 알고리즘</t>
-        </is>
-      </c>
+          <t>그럼에도 불구하고 나는 내가 좋았어</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>다우치 마나부 (지은이), 김슬기 (옮긴이)</t>
+          <t>박채린 (지은이)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>19800</v>
+        <v>18000</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>9791193937068</t>
+          <t>9791193937105</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363272157</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=340511549</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>똑똑한 아이는 어떻게 생각하고 질문하는가</t>
+          <t>부자의 마지막 가르침 (30만 부 리커버)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>사고력 실종의 시대, 주도적인 아이들의 생존 전략</t>
+          <t>삶의 자유를 위한 부의 알고리즘</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>이시한 (지은이)</t>
+          <t>다우치 마나부 (지은이), 김슬기 (옮긴이)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>북크레용</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>자녀교육</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -4331,89 +4331,89 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>9791193937037</t>
+          <t>9791193937068</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=337128010</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363272157</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>사랑받는 이기주의자</t>
+          <t>똑똑한 아이는 어떻게 생각하고 질문하는가</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>나를 지키며 사랑받는 관계의 기술</t>
+          <t>사고력 실종의 시대, 주도적인 아이들의 생존 전략</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>박코 (지은이)</t>
+          <t>이시한 (지은이)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북크레용</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>자녀교육</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>18000</v>
+        <v>19800</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>9791193937051</t>
+          <t>9791193937037</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=338458067</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=337128010</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>내가 천 개의 인생에서 배운 것들</t>
+          <t>사랑받는 이기주의자</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>돈, 명예, 시간 그 무엇보다 소중한 것에 관하여</t>
+          <t>나를 지키며 사랑받는 관계의 기술</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>김도윤 (지은이)</t>
+          <t>박코 (지은이)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -4421,79 +4421,79 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>9791198530394</t>
+          <t>9791193937051</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=337269711</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=338458067</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>양수인간</t>
+          <t>내가 천 개의 인생에서 배운 것들</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>삶의 격을 높이는 내면 변화 심리학</t>
+          <t>돈, 명예, 시간 그 무엇보다 소중한 것에 관하여</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>최설민 (지은이)</t>
+          <t>김도윤 (지은이)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>19800</v>
+        <v>18000</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>9791193937006</t>
+          <t>9791198530394</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=336173615</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=337269711</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>무엇이 나를 행복하게 만드는가</t>
+          <t>양수인간</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>인생의 절반쯤 왔을 때 깨닫게 되는 것들</t>
+          <t>삶의 격을 높이는 내면 변화 심리학</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>리처드 J. 라이더, 데이비드 A. 샤피로 (지은이), 김정홍 (옮긴이)</t>
+          <t>최설민 (지은이)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -4511,29 +4511,29 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>9791198530356</t>
+          <t>9791193937006</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=334885758</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=336173615</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>노인의 꿈 : 첫 번째 이야기</t>
+          <t>무엇이 나를 행복하게 만드는가</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>황혼을 향해 걷는 우리 모두의 이야기</t>
+          <t>인생의 절반쯤 왔을 때 깨닫게 되는 것들</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>백원달 (지은이)</t>
+          <t>리처드 J. 라이더, 데이비드 A. 샤피로 (지은이), 김정홍 (옮긴이)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4543,32 +4543,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>그 밖의 책</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>23000</v>
+        <v>19800</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>9791191891478</t>
+          <t>9791198530356</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=335184922</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=334885758</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>노인의 꿈 : 두 번째 이야기</t>
+          <t>노인의 꿈 : 첫 번째 이야기</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4601,29 +4601,29 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>9791191891485</t>
+          <t>9791191891478</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=335185323</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=335184922</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>똑똑한 사람은 어떻게 생각하고 질문하는가</t>
+          <t>노인의 꿈 : 두 번째 이야기</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>사고력 실종의 시대, 앞서가는 사람들의 생존 전략</t>
+          <t>황혼을 향해 걷는 우리 모두의 이야기</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>이시한 (지은이)</t>
+          <t>백원달 (지은이)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4633,42 +4633,42 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>그 밖의 책</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>19800</v>
+        <v>23000</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>9791191891492</t>
+          <t>9791191891485</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=332269449</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=335185323</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>산책하듯 가볍게 (풀빛 에디션)</t>
+          <t>똑똑한 사람은 어떻게 생각하고 질문하는가</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>인생에서 여유를 찾는 당신에게 건네는 말</t>
+          <t>사고력 실종의 시대, 앞서가는 사람들의 생존 전략</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>정우성 (지은이)</t>
+          <t>이시한 (지은이)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4678,47 +4678,47 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>17500</v>
+        <v>19800</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>9791191891447</t>
+          <t>9791191891492</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=388109982</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=332269449</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>하는 일마다 잘되리라</t>
+          <t>산책하듯 가볍게 (풀빛 에디션)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>당신이 어디에 있든 무엇을 하든</t>
+          <t>인생에서 여유를 찾는 당신에게 건네는 말</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>전승환 (지은이)</t>
+          <t>정우성 (지은이)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4728,127 +4728,127 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>18000</v>
+        <v>17500</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>9791198530301</t>
+          <t>9791191891447</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=328632910</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=388109982</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>머니 트렌드 2024</t>
+          <t>하는 일마다 잘되리라</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>57가지 키워드로 전망하는 대한민국 돈의 흐름</t>
+          <t>당신이 어디에 있든 무엇을 하든</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>김도윤, 정태익, 김용섭, 김현준, 전영수, 채상욱, 최재붕, 홍춘욱 (지은이)</t>
+          <t>전승환 (지은이)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>25000</v>
+        <v>18000</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>9791191891416</t>
+          <t>9791198530301</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=324498127</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=328632910</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>꽃은 누구에게나 핀다</t>
+          <t>머니 트렌드 2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>오늘부터 내 삶을 바꾸는 자기 확신 에세이, 매일 더 설레는 날을 살게 될 당신에</t>
+          <t>57가지 키워드로 전망하는 대한민국 돈의 흐름</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>오은환 (지은이)</t>
+          <t>김도윤, 정태익, 김용섭, 김현준, 전영수, 채상욱, 최재붕, 홍춘욱 (지은이)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>17500</v>
+        <v>25000</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>9791191891409</t>
+          <t>9791191891416</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=324723810</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=324498127</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>나는 너랑 노는 게 제일 좋아</t>
+          <t>꽃은 누구에게나 핀다</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>아끼고 고맙고 사랑하는 당신에게</t>
+          <t>오늘부터 내 삶을 바꾸는 자기 확신 에세이, 매일 더 설레는 날을 살게 될 당신에</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>하태완 (지은이)</t>
+          <t>오은환 (지은이)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -4871,29 +4871,29 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>9791191891362</t>
+          <t>9791191891409</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=320503944</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=324723810</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>마음의 자유</t>
+          <t>나는 너랑 노는 게 제일 좋아</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>행복이란 마음이 어디에도 얽매이지 않는 것</t>
+          <t>아끼고 고맙고 사랑하는 당신에게</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>정윤 (지은이)</t>
+          <t>하태완 (지은이)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4908,37 +4908,37 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>17000</v>
+        <v>17500</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>9791191891355</t>
+          <t>9791191891362</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=318438169</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=320503944</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>찌그러져도 괜찮아</t>
+          <t>마음의 자유</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>이미 찌그러진 오리가</t>
+          <t>행복이란 마음이 어디에도 얽매이지 않는 것</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>찌오(임임) (지은이)</t>
+          <t>정윤 (지은이)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -4961,35 +4961,39 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>9791191891324</t>
+          <t>9791191891355</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=315987317</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=318438169</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>인생에서 가장 후회되는 게 뭐냐고 묻는다면</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
+          <t>찌그러져도 괜찮아</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>이미 찌그러진 오리가</t>
+        </is>
+      </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>노우티 (지은이)</t>
+          <t>찌오(임임) (지은이)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4998,156 +5002,156 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>17500</v>
+        <v>17000</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>9791191891331</t>
+          <t>9791191891324</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=315418702</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=315987317</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>당신과 아침에 싸우면 밤에는 입맞출 겁니다</t>
+          <t>인생에서 가장 후회되는 게 뭐냐고 묻는다면</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>유래혁 (지은이)</t>
+          <t>노우티 (지은이)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>17000</v>
+        <v>17500</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>9791191891263</t>
+          <t>9791191891331</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=313695065</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=315418702</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GPT 제너레이션 : 챗GPT가 바꿀 우리 인류의 미래</t>
+          <t>당신과 아침에 싸우면 밤에는 입맞출 겁니다</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>이시한 (지은이)</t>
+          <t>유래혁 (지은이)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>19000</v>
+        <v>17000</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>9791191891270</t>
+          <t>9791191891263</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=310813322</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=313695065</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>오둥이입니다만!</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>나는 세상에서 가장 행복한 오리</t>
-        </is>
-      </c>
+          <t>GPT 제너레이션 : 챗GPT가 바꿀 우리 인류의 미래</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>송 스튜디오 (지은이)</t>
+          <t>이시한 (지은이)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>17000</v>
+        <v>19000</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>9791191891256</t>
+          <t>9791191891270</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=310407734</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=310813322</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>행복을 담아줄게</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
+          <t>오둥이입니다만!</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>나는 세상에서 가장 행복한 오리</t>
+        </is>
+      </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>나란 (지은이)</t>
+          <t>송 스튜디오 (지은이)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5162,37 +5166,33 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>16000</v>
+        <v>17000</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>9791191891249</t>
+          <t>9791191891256</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=309568882</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=310407734</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>나는 오늘의 내가 좋아</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>긍정토끼 몰랑이의 몰랑몰랑 마음 일기</t>
-        </is>
-      </c>
+          <t>행복을 담아줄게</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>윤혜지(하얀오리) (지은이)</t>
+          <t>나란 (지은이)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2023-01-30</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -5215,111 +5215,115 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>9791191891126</t>
+          <t>9791191891249</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=306216745</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=309568882</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>머니 트렌드 2023</t>
+          <t>나는 오늘의 내가 좋아</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>45가지 키워드로 전망하는 대한민국 돈의 흐름</t>
+          <t>긍정토끼 몰랑이의 몰랑몰랑 마음 일기</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>부동산읽어주는남자(정태익), 김도윤, 김경민, 김상균, 전영수, 최준철, 홍춘욱 (지은이)</t>
+          <t>윤혜지(하얀오리) (지은이)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>19000</v>
+        <v>16000</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>9791191891232</t>
+          <t>9791191891126</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=304588805</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=306216745</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>잘될 수밖에 없는 너에게</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
+          <t>머니 트렌드 2023</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>45가지 키워드로 전망하는 대한민국 돈의 흐름</t>
+        </is>
+      </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>최서영 (지은이)</t>
+          <t>부동산읽어주는남자(정태익), 김도윤, 김경민, 김상균, 전영수, 최준철, 홍춘욱 (지은이)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>19500</v>
+        <v>19000</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>9791191891201</t>
+          <t>9791191891232</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=299808248</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=304588805</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>나로서 충분히 괜찮은 사람</t>
+          <t>잘될 수밖에 없는 너에게</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>김재식 (지은이)</t>
+          <t>최서영 (지은이)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5334,37 +5338,33 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>16000</v>
+        <v>19500</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>9791191891096</t>
+          <t>9791191891201</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=294392417</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=299808248</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>나에게 고맙다</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>30만 부 기념 전면개정판</t>
-        </is>
-      </c>
+          <t>나로서 충분히 괜찮은 사람</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>전승환 (지은이)</t>
+          <t>김재식 (지은이)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5379,37 +5379,37 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>2022-05-10</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>19000</v>
+        <v>16000</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>9791191891072</t>
+          <t>9791191891096</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=289269041</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=294392417</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>럭키 LUCKY</t>
+          <t>나에게 고맙다</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>내 안에 잠든 운을 깨우는 7가지 법칙</t>
+          <t>30만 부 기념 전면개정판</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>김도윤 (지은이)</t>
+          <t>전승환 (지은이)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5419,42 +5419,42 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>9791191891027</t>
+          <t>9791191891072</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=278177114</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=289269041</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>그렇다면 나를 응원할 수밖에 (윈터 에디션)</t>
+          <t>럭키 LUCKY</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>멋대로지만 제대로 사는 중입니다</t>
+          <t>내 안에 잠든 운을 깨우는 7가지 법칙</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>김수민 (지은이)</t>
+          <t>김도윤 (지은이)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5464,38 +5464,42 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
+          <t>2021-08-25</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>9791197037191</t>
+          <t>9791191891027</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=283440909</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=278177114</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>작은 별이지만 빛나고 있어 (30만부 기념 미드나잇 에디션)</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
+          <t>그렇다면 나를 응원할 수밖에 (윈터 에디션)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>멋대로지만 제대로 사는 중입니다</t>
+        </is>
+      </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>소윤 (지은이)</t>
+          <t>김수민 (지은이)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5510,33 +5514,33 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>19000</v>
+        <v>15000</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>9791197037153</t>
+          <t>9791197037191</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=367659804</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=283440909</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>좋은 건 같이 봐요</t>
+          <t>작은 별이지만 빛나고 있어 (30만부 기념 미드나잇 에디션)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>엄지사진관 (지은이)</t>
+          <t>소윤 (지은이)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5551,33 +5555,33 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2021-01-27</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>15000</v>
+        <v>19000</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>9791197037146</t>
+          <t>9791197037153</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=262375795</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=367659804</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>안녕, 소중한 사람</t>
+          <t>좋은 건 같이 봐요</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>정한경 (지은이)</t>
+          <t>엄지사진관 (지은이)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5592,63 +5596,104 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2021-01-27</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>19000</v>
+        <v>15000</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>9791197037122</t>
+          <t>9791197037146</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=251524184</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=262375795</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>안녕, 소중한 사람</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>정한경 (지은이)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>북로망스</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>에세이</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>19000</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>9791197037122</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=251524184</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>나는 나를 사랑한다</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>나를 잃지 않고 타인을 사랑하기 위하여</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>이숙명 (지은이)</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>북로망스</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>에세이</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>2020-06-24</t>
         </is>
       </c>
-      <c r="G120" t="n">
+      <c r="G121" t="n">
         <v>14800</v>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>9791197037108</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=242494208</t>
         </is>

--- a/files/thebookman-booklist.xlsx
+++ b/files/thebookman-booklist.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -490,17 +490,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>다정한 안녕</t>
+          <t>나답게 똘똘하게</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>달콤하고도 먹먹한 우리의 이별 준비</t>
+          <t>정답 없는 세상에서 나로 온전히 살아가는 법</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>마크 스티븐 포로 (지은이), 이유림 (옮긴이)</t>
+          <t>김똘똘(김반석) (지은이)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -515,33 +515,37 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>22000</v>
+        <v>19800</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>9791124038932</t>
+          <t>9791124038956</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=403874634</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=405062863</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>품격 있는 대화를 위한 지식 브리핑 (10만 부 기념 특별 한정판)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>다정한 안녕</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>달콤하고도 먹먹한 우리의 이별 준비</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>김진 (지은이)</t>
+          <t>마크 스티븐 포로 (지은이), 이유림 (옮긴이)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -551,79 +555,79 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>25000</v>
+        <v>22000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9791124038413</t>
+          <t>9791124038932</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=404263026</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=403874634</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>여름</t>
+          <t>품격 있는 대화를 위한 지식 브리핑 (10만 부 기념 특별 한정판)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>이디스 워튼 (지은이), 민지현 (옮긴이)</t>
+          <t>김진 (지은이)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>머묾</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>19000</v>
+        <v>25000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9791124038802</t>
+          <t>9791124038413</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401985055</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=404263026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>위대한 개츠비</t>
+          <t>여름</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>프랜시스 스콧 피츠제럴드 (지은이), 이미정 (옮긴이)</t>
+          <t>이디스 워튼 (지은이), 민지현 (옮긴이)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -646,25 +650,25 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9791124038659</t>
+          <t>9791124038802</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401984756</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401985055</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파리는 언제나 축제</t>
+          <t>위대한 개츠비</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>어니스트 헤밍웨이 (지은이), 권진아 (옮긴이)</t>
+          <t>프랜시스 스콧 피츠제럴드 (지은이), 이미정 (옮긴이)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -674,7 +678,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -687,39 +691,35 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9791124038666</t>
+          <t>9791124038659</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401985497</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401984756</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>단단히, 휩쓸리지 않고 살아간다는 것</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>흔들리는 시간을 지혜롭게 건너는 마음의 철학</t>
-        </is>
-      </c>
+          <t>파리는 언제나 축제</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>나디 미리안 (지은이), 김지유 (옮긴이)</t>
+          <t>어니스트 헤밍웨이 (지은이), 권진아 (옮긴이)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>머묾</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -728,88 +728,88 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9791124038888</t>
+          <t>9791124038666</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=403488397</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401985497</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>머니 트렌드 2027</t>
+          <t>단단히, 휩쓸리지 않고 살아간다는 것</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>격변의 위기를 기회로 바꾸는 55가지 돈의 흐름</t>
+          <t>흔들리는 시간을 지혜롭게 건너는 마음의 철학</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>정태익, 김도윤, 김광석, 김용섭, 김학렬, 박세익, 박정호, 이효석 (지은이)</t>
+          <t>나디 미리안 (지은이), 김지유 (옮긴이)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>27500</v>
+        <v>22000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9791124038826</t>
+          <t>9791124038888</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401122536</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=403488397</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>처음 만나는 철학의 세계</t>
+          <t>머니 트렌드 2027</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>삶에 철학이 들어오는 순간</t>
+          <t>격변의 위기를 기회로 바꾸는 55가지 돈의 흐름</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>성창원 (지은이)</t>
+          <t>정태익, 김도윤, 김광석, 김용섭, 김학렬, 박세익, 박정호, 이효석 (지은이)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -818,33 +818,33 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>22000</v>
+        <v>27500</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9791124038833</t>
+          <t>9791124038826</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=402017704</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401122536</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>똑똑한 사람은 어떻게 말하는가</t>
+          <t>처음 만나는 철학의 세계</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>길게 말하지 않아도 신뢰받는 사람들의 말하기 전략</t>
+          <t>삶에 철학이 들어오는 순간</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>이시한 (지은이)</t>
+          <t>성창원 (지은이)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -867,171 +867,175 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9791124038642</t>
+          <t>9791124038833</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=400007561</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=402017704</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>기억의 무늬</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>똑똑한 사람은 어떻게 말하는가</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>길게 말하지 않아도 신뢰받는 사람들의 말하기 전략</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>백희성 (지은이)</t>
+          <t>이시한 (지은이)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>19800</v>
+        <v>22000</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9791124038604</t>
+          <t>9791124038642</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=398993923</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=400007561</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>나는 도대체 왜 눈치를 볼까</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>타인의 기대에서 벗어나 원하는 삶을 사는 법</t>
-        </is>
-      </c>
+          <t>기억의 무늬</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>케리 올리치, 켈리 권터 (지은이), 김잔디 (옮긴이)</t>
+          <t>백희성 (지은이)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>21000</v>
+        <v>19800</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9791124038536</t>
+          <t>9791124038604</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=397995935</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=398993923</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>만일 나에게 단 한 번의 아침이 남아 있다면 (굿모닝 에디션)</t>
+          <t>나는 도대체 왜 눈치를 볼까</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>오늘이 끝나기 전 반드시 깨달아야 할 것들</t>
+          <t>타인의 기대에서 벗어나 원하는 삶을 사는 법</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>존 릴런드 (지은이), 최인하 (옮긴이)</t>
+          <t>케리 올리치, 켈리 권터 (지은이), 김잔디 (옮긴이)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>19800</v>
+        <v>21000</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9791193937112</t>
+          <t>9791124038536</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=398820063</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=397995935</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>너의 행복은 나의 기쁨이야</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>만일 나에게 단 한 번의 아침이 남아 있다면 (굿모닝 에디션)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>오늘이 끝나기 전 반드시 깨달아야 할 것들</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>정한경 (지은이)</t>
+          <t>존 릴런드 (지은이), 최인하 (옮긴이)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1039,80 +1043,76 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9791124038574</t>
+          <t>9791193937112</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396794390</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=398820063</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>여름 (썸머 에디션)</t>
+          <t>너의 행복은 나의 기쁨이야</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>이디스 워튼 (지은이), 민지현 (옮긴이)</t>
+          <t>정한경 (지은이)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>머묾</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>19000</v>
+        <v>19800</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9791124038581</t>
+          <t>9791124038574</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396568091</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396794390</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>끌리는 사람의 비밀</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>마음을 움직이는 품위 있는 말과 태도</t>
-        </is>
-      </c>
+          <t>여름 (썸머 에디션)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>조수빈 (지은이)</t>
+          <t>이디스 워튼 (지은이), 민지현 (옮긴이)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>머묾</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1121,38 +1121,38 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9791124038567</t>
+          <t>9791124038581</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396156367</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396568091</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>최소한의 습관</t>
+          <t>끌리는 사람의 비밀</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>작은 시작으로 압도적 변화를 만드는 행동 공식</t>
+          <t>마음을 움직이는 품위 있는 말과 태도</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>로버트 마우어 (지은이), 장원철 (옮긴이)</t>
+          <t>조수빈 (지은이)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1162,74 +1162,78 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>19800</v>
+        <v>22000</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9791124038512</t>
+          <t>9791124038567</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=394919714</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396156367</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>이방인</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>최소한의 습관</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>작은 시작으로 압도적 변화를 만드는 행동 공식</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>알베르 카뮈 (지은이), 한수민 (옮긴이)</t>
+          <t>로버트 마우어 (지은이), 장원철 (옮긴이)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>머묾</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>18000</v>
+        <v>19800</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9791124038390</t>
+          <t>9791124038512</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396164215</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=394919714</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>프랑켄슈타인</t>
+          <t>이방인</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>메리 셸리 (지은이), 이미애 (옮긴이)</t>
+          <t>알베르 카뮈 (지은이), 한수민 (옮긴이)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1248,29 +1252,29 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>21000</v>
+        <v>18000</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9791124038383</t>
+          <t>9791124038390</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396166191</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396164215</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>올랜도</t>
+          <t>프랑켄슈타인</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>버지니아 울프 (지은이), 정해영 (옮긴이)</t>
+          <t>메리 셸리 (지은이), 이미애 (옮긴이)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1289,34 +1293,34 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>20000</v>
+        <v>21000</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9791124038406</t>
+          <t>9791124038383</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396167382</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396166191</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>리치먼드힐의 이층 버스</t>
+          <t>올랜도</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>이경진 (지은이)</t>
+          <t>버지니아 울프 (지은이), 정해영 (옮긴이)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>머묾</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1330,441 +1334,437 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>9791124038499</t>
+          <t>9791124038406</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=394084608</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396167382</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>밤의 설계자</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>잠들기 전 15분, 미래를 바꾸는 밤 생각 습관</t>
-        </is>
-      </c>
+          <t>리치먼드힐의 이층 버스</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>폴커 부슈 (지은이), 이상희 (옮긴이)</t>
+          <t>이경진 (지은이)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>9791124038468</t>
+          <t>9791124038499</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=393318252</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=394084608</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>웨딩 피플</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>밤의 설계자</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>잠들기 전 15분, 미래를 바꾸는 밤 생각 습관</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>앨리슨 에스파흐 (지은이), 김보람 (옮긴이)</t>
+          <t>폴커 부슈 (지은이), 이상희 (옮긴이)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>9791124038437</t>
+          <t>9791124038468</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=392621945</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=393318252</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>아우슈비츠의 무용수</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>인생은 언제나 다시 선택할 수 있다</t>
-        </is>
-      </c>
+          <t>웨딩 피플</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>에디트 에바 에거 (지은이), 안진희 (옮긴이)</t>
+          <t>앨리슨 에스파흐 (지은이), 김보람 (옮긴이)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>24000</v>
+        <v>21000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>9791124038352</t>
+          <t>9791124038437</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=391538652</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=392621945</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>오리지널 코드</t>
+          <t>아우슈비츠의 무용수</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>상위 1%의 비밀, 나답게 일하고 나답게 성공하는 절대 공식</t>
+          <t>인생은 언제나 다시 선택할 수 있다</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>오은환 (지은이)</t>
+          <t>에디트 에바 에거 (지은이), 안진희 (옮긴이)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>9791124038369</t>
+          <t>9791124038352</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=390350168</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=391538652</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>미스터 나카모토</t>
+          <t>오리지널 코드</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>비트코인의 창시자</t>
+          <t>상위 1%의 비밀, 나답게 일하고 나답게 성공하는 절대 공식</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>벤저민 윌리스 (지은이), 이재득 (옮긴이)</t>
+          <t>오은환 (지은이)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>25000</v>
+        <v>22000</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>9791124038314</t>
+          <t>9791124038369</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=387309381</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=390350168</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>바다에서 온 소년</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>미스터 나카모토</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>비트코인의 창시자</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개럿 카 (지은이), 이은선 (옮긴이)</t>
+          <t>벤저민 윌리스 (지은이), 이재득 (옮긴이)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>19800</v>
+        <v>25000</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>9791124038338</t>
+          <t>9791124038314</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=388570776</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=387309381</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>사람을 얻는 힘 : 인간력</t>
+          <t>바다에서 온 소년</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>다사카 히로시 (지은이), 장은주 (옮긴이)</t>
+          <t>개럿 카 (지은이), 이은선 (옮긴이)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>20000</v>
+        <v>19800</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>9791124038253</t>
+          <t>9791124038338</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=387645690</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=388570776</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>당신은 가치 있다</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>마음을 회복하는 자기 돌봄의 심리학</t>
-        </is>
-      </c>
+          <t>사람을 얻는 힘 : 인간력</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>안드레아스 크누프 (지은이), 박병화 (옮긴이)</t>
+          <t>다사카 히로시 (지은이), 장은주 (옮긴이)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>19800</v>
+        <v>20000</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9791124038291</t>
+          <t>9791124038253</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=386487867</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=387645690</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>삶의 끝에서 만난 수업</t>
+          <t>당신은 가치 있다</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>죽음이 가르쳐준 후회 없는 삶</t>
+          <t>마음을 회복하는 자기 돌봄의 심리학</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>에리카 하야사키 (지은이), 이은주 (옮긴이)</t>
+          <t>안드레아스 크누프 (지은이), 박병화 (옮긴이)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>22000</v>
+        <v>19800</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9791124038284</t>
+          <t>9791124038291</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=385616736</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=386487867</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>모든 것은 별에서 시작되었다</t>
+          <t>삶의 끝에서 만난 수업</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>천문학자가 바라본 우주와 인류의 발자취</t>
+          <t>죽음이 가르쳐준 후회 없는 삶</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>조앤 베이커 (지은이), 고유경 (옮긴이)</t>
+          <t>에리카 하야사키 (지은이), 이은주 (옮긴이)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1772,44 +1772,44 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9791124038277</t>
+          <t>9791124038284</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=385203905</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=385616736</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>모두에게 사랑받을 필요는 없다</t>
+          <t>모든 것은 별에서 시작되었다</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>비교와 눈치에서 해방되는 삶의 기술</t>
+          <t>천문학자가 바라본 우주와 인류의 발자취</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>웨인 다이어 (지은이), 장원철 (옮긴이)</t>
+          <t>조앤 베이커 (지은이), 고유경 (옮긴이)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1817,71 +1817,75 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>9791124038185</t>
+          <t>9791124038277</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384701650</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=385203905</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>나의 완벽한 장례식</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>모두에게 사랑받을 필요는 없다</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>비교와 눈치에서 해방되는 삶의 기술</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>조현선 (지은이)</t>
+          <t>웨인 다이어 (지은이), 장원철 (옮긴이)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>19000</v>
+        <v>22000</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>9791124038192</t>
+          <t>9791124038185</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=383575374</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384701650</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>첫눈, 고백</t>
+          <t>나의 완벽한 장례식</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>기 드 모파상 (지은이), 구영옥 (옮긴이)</t>
+          <t>조현선 (지은이)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>머묾</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1891,7 +1895,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1899,25 +1903,25 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>9791124038154</t>
+          <t>9791124038192</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=381528041</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=383575374</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>사랑에 관한 짧은 이야기</t>
+          <t>첫눈, 고백</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>프랜시스 스콧 피츠제럴드 (지은이), 정지현 (옮긴이)</t>
+          <t>기 드 모파상 (지은이), 구영옥 (옮긴이)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1940,25 +1944,25 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>9791124038161</t>
+          <t>9791124038154</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=381620936</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=381528041</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>첫사랑</t>
+          <t>사랑에 관한 짧은 이야기</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>이반 세르게예비치 투르게네프 (지은이), 승주연 (옮긴이)</t>
+          <t>프랜시스 스콧 피츠제럴드 (지은이), 정지현 (옮긴이)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1977,93 +1981,89 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>18000</v>
+        <v>19000</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>9791124038147</t>
+          <t>9791124038161</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=381528407</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=381620936</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>캘리쌤의 루틴 잉글리시</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>하루 10분, 90일 영어 습관 프로젝트</t>
-        </is>
-      </c>
+          <t>첫사랑</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>캘리쌤 (지은이)</t>
+          <t>이반 세르게예비치 투르게네프 (지은이), 승주연 (옮긴이)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>머묾</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>그 밖의 책</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9791124038123</t>
+          <t>9791124038147</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=379524547</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=381528407</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>마일리지 아워</t>
+          <t>캘리쌤의 루틴 잉글리시</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>삶의 격을 높이는 인생 설계의 기술</t>
+          <t>하루 10분, 90일 영어 습관 프로젝트</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>최유나 (지은이)</t>
+          <t>캘리쌤 (지은이)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>그 밖의 책</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2071,29 +2071,29 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>9791124038093</t>
+          <t>9791124038123</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=377166373</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=379524547</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>석세스</t>
+          <t>마일리지 아워</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>지금 시작하는 목표 설계의 비밀</t>
+          <t>삶의 격을 높이는 인생 설계의 기술</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>하이디 그랜트 할버슨 (지은이), 장원철 (옮긴이)</t>
+          <t>최유나 (지은이)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2108,68 +2108,72 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>9791124038086</t>
+          <t>9791124038093</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=374615177</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=377166373</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 10</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>석세스</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>지금 시작하는 목표 설계의 비밀</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>나관중 (지은이), 백남원 (그림), 박상률 (옮긴이)</t>
+          <t>하이디 그랜트 할버슨 (지은이), 장원철 (옮긴이)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>18800</v>
+        <v>21000</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>9791193937969</t>
+          <t>9791124038086</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384185742</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=374615177</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 9</t>
+          <t>박상률 완역 삼국지 10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2198,19 +2202,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>9791193937952</t>
+          <t>9791193937969</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384185675</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384185742</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 8</t>
+          <t>박상률 완역 삼국지 9</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2239,19 +2243,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>9791193937945</t>
+          <t>9791193937952</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184694</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384185675</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 7</t>
+          <t>박상률 완역 삼국지 8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2280,19 +2284,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>9791193937938</t>
+          <t>9791193937945</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184639</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184694</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 6</t>
+          <t>박상률 완역 삼국지 7</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2321,19 +2325,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>9791193937921</t>
+          <t>9791193937938</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184552</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184639</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 5</t>
+          <t>박상률 완역 삼국지 6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2362,19 +2366,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>9791193937914</t>
+          <t>9791193937921</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184384</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184552</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 4</t>
+          <t>박상률 완역 삼국지 5</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2403,19 +2407,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>9791193937907</t>
+          <t>9791193937914</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184368</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184384</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 3</t>
+          <t>박상률 완역 삼국지 4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2444,19 +2448,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>9791193937891</t>
+          <t>9791193937907</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184313</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184368</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 2</t>
+          <t>박상률 완역 삼국지 3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2485,19 +2489,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>9791193937884</t>
+          <t>9791193937891</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184247</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184313</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 1</t>
+          <t>박상률 완역 삼국지 2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2526,26 +2530,22 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>9791193937877</t>
+          <t>9791193937884</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384183907</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184247</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 세트</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>전10권</t>
-        </is>
-      </c>
+          <t>박상률 완역 삼국지 1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>나관중 (지은이), 백남원 (그림), 박상률 (옮긴이)</t>
@@ -2567,33 +2567,33 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>188000</v>
+        <v>18800</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>9791193937860</t>
+          <t>9791193937877</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384182721</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384183907</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>때로 외로움은 삶의 방패가 된다</t>
+          <t>박상률 완역 삼국지 세트</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>타인에게 상처받지 않고 나를 지키는 고독의 힘</t>
+          <t>전10권</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>에노모토 히로아키 (지은이), 장은주 (옮긴이)</t>
+          <t>나관중 (지은이), 백남원 (그림), 박상률 (옮긴이)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2612,89 +2612,89 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>19000</v>
+        <v>188000</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>9791124038024</t>
+          <t>9791193937860</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=374895246</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384182721</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>브로큰 컨트리</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>때로 외로움은 삶의 방패가 된다</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>타인에게 상처받지 않고 나를 지키는 고독의 힘</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>클레어 레슬리 홀 (지은이), 박지선 (옮긴이)</t>
+          <t>에노모토 히로아키 (지은이), 장은주 (옮긴이)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>19500</v>
+        <v>19000</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>9791193937853</t>
+          <t>9791124038024</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=373453855</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=374895246</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>어른의 품위</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>진짜 어른이 되기 위해 지켜야 할 삶의 태도</t>
-        </is>
-      </c>
+          <t>브로큰 컨트리</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>최서영 (지은이)</t>
+          <t>클레어 레슬리 홀 (지은이), 박지선 (옮긴이)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -2702,119 +2702,119 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>9791193937693</t>
+          <t>9791193937853</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=372567841</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=373453855</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>머니 트렌드 2026</t>
+          <t>어른의 품위</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>위기 속 돈의 흐름을 지배하는 50가지 생존 공식</t>
+          <t>진짜 어른이 되기 위해 지켜야 할 삶의 태도</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>김도윤, 정태익, 김광석, 김승주, 김용섭, 김학렬(빠숑), 김현준, 최재붕 (지은이)</t>
+          <t>최서영 (지은이)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>9791193937686</t>
+          <t>9791193937693</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=370922288</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=372567841</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>처음 만나는 양자의 세계</t>
+          <t>머니 트렌드 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>양자 역학부터 양자 컴퓨터 까지</t>
+          <t>위기 속 돈의 흐름을 지배하는 50가지 생존 공식</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>채은미 (지은이)</t>
+          <t>김도윤, 정태익, 김광석, 김승주, 김용섭, 김학렬(빠숑), 김현준, 최재붕 (지은이)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>19000</v>
+        <v>26000</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>9791193937990</t>
+          <t>9791193937686</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=372088796</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=370922288</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>파이브 센스</t>
+          <t>처음 만나는 양자의 세계</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>소진된 일상에서 행복을 되찾는 마음 회복법</t>
+          <t>양자 역학부터 양자 컴퓨터 까지</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>그레첸 루빈 (지은이), 김잔디 (옮긴이)</t>
+          <t>채은미 (지은이)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2824,128 +2824,128 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>9791193937846</t>
+          <t>9791193937990</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=369930840</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=372088796</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>월요일 수요일 토요일</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>파이브 센스</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>소진된 일상에서 행복을 되찾는 마음 회복법</t>
+        </is>
+      </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>페트라 펠리니 (지은이), 전은경 (옮긴이)</t>
+          <t>그레첸 루빈 (지은이), 김잔디 (옮긴이)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>19500</v>
+        <v>22000</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>9791193937822</t>
+          <t>9791193937846</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=369095688</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=369930840</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>시선 너머의 지식</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>9가지 질문으로 읽는 숨겨진 세계</t>
-        </is>
-      </c>
+          <t>월요일 수요일 토요일</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>윤수용 (지은이)</t>
+          <t>페트라 펠리니 (지은이), 전은경 (옮긴이)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>22000</v>
+        <v>19500</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>9791193937785</t>
+          <t>9791193937822</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=368128493</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=369095688</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>행복 강박</t>
+          <t>시선 너머의 지식</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>행복 과잉 시대에서 잃어버린 진짜 삶을 찾는 법</t>
+          <t>9가지 질문으로 읽는 숨겨진 세계</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>올리버 버크먼 (지은이), 정지인 (옮긴이)</t>
+          <t>윤수용 (지은이)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2968,67 +2968,71 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>9791193937778</t>
+          <t>9791193937785</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=366392151</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=368128493</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>메리골드 아틀리에 컬렉션 특별 한정판 세트</t>
+          <t>행복 강박</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>전3권</t>
+          <t>행복 과잉 시대에서 잃어버린 진짜 삶을 찾는 법</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>윤정은 (지은이)</t>
+          <t>올리버 버크먼 (지은이), 정지인 (옮긴이)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>54000</v>
+        <v>22000</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>9791193937754</t>
+          <t>9791193937778</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365445143</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=366392151</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>메리골드 마음 식물원 (아틀리에 컬렉션)</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>메리골드 아틀리에 컬렉션 특별 한정판 세트</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>전3권</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
           <t>윤정은 (지은이)</t>
@@ -3050,23 +3054,23 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>18000</v>
+        <v>54000</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>9791193937723</t>
+          <t>9791193937754</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365443154</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365445143</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>메리골드 마음 사진관 (아틀리에 컬렉션)</t>
+          <t>메리골드 마음 식물원 (아틀리에 컬렉션)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -3095,19 +3099,19 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>9791193937730</t>
+          <t>9791193937723</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365443349</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365443154</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>메리골드 마음 세탁소 (아틀리에 컬렉션)</t>
+          <t>메리골드 마음 사진관 (아틀리에 컬렉션)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -3136,220 +3140,220 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>9791193937310</t>
+          <t>9791193937730</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365443113</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365443349</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>왓츠 유어 드림</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>인생을 뒤바꾸는 단 하나의 질문</t>
-        </is>
-      </c>
+          <t>메리골드 마음 세탁소 (아틀리에 컬렉션)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>사이먼 스큅 (지은이), 최인하 (옮긴이)</t>
+          <t>윤정은 (지은이)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>9791193937709</t>
+          <t>9791193937310</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=364723142</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365443113</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>우리의 낙원에서 만나자</t>
+          <t>왓츠 유어 드림</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>이 계절을 함께 건너는 당신에게</t>
+          <t>인생을 뒤바꾸는 단 하나의 질문</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>하태완 (지은이)</t>
+          <t>사이먼 스큅 (지은이), 최인하 (옮긴이)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>19500</v>
+        <v>22000</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>9791193937655</t>
+          <t>9791193937709</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363874338</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=364723142</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>코어 씽킹 Core Thinking</t>
+          <t>우리의 낙원에서 만나자</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>일의 본질을 꿰뚫는 생각의 기술</t>
+          <t>이 계절을 함께 건너는 당신에게</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>김범섭 (지은이)</t>
+          <t>하태완 (지은이)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>22000</v>
+        <v>19500</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>9791193937624</t>
+          <t>9791193937655</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363358764</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363874338</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>당신은 언제나 괜찮다</t>
+          <t>코어 씽킹 Core Thinking</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>흔들리는 시간을 넘어 단단히 나를 세우는 법</t>
+          <t>일의 본질을 꿰뚫는 생각의 기술</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>이현수 (지은이)</t>
+          <t>김범섭 (지은이)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>19800</v>
+        <v>22000</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>9791193937617</t>
+          <t>9791193937624</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363057823</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363358764</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>다 좋아질 거야, 행복이 쏟아질 만큼</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>당신은 언제나 괜찮다</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>흔들리는 시간을 넘어 단단히 나를 세우는 법</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>길연우 (지은이)</t>
+          <t>이현수 (지은이)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -3357,89 +3361,85 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>9791193937594</t>
+          <t>9791193937617</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=362220234</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363057823</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>무엇을 사랑하고 어떻게 행복할 것인가</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>행복을 습관으로 만드는 하버드 명강의</t>
-        </is>
-      </c>
+          <t>다 좋아질 거야, 행복이 쏟아질 만큼</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>유키 소노마 (지은이), 정은희 (옮긴이)</t>
+          <t>길연우 (지은이)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>22000</v>
+        <v>19800</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>9791193937587</t>
+          <t>9791193937594</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=361430765</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=362220234</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>나를 쓰는 시간</t>
+          <t>무엇을 사랑하고 어떻게 행복할 것인가</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>한 줄의 기록이 삶을 바꾼다</t>
+          <t>행복을 습관으로 만드는 하버드 명강의</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>장예원 (지은이)</t>
+          <t>유키 소노마 (지은이), 정은희 (옮긴이)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -3447,70 +3447,70 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>9791193937365</t>
+          <t>9791193937587</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=361643111</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=361430765</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>모든 걸음에는 이유가 있다</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>나를 쓰는 시간</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>한 줄의 기록이 삶을 바꾼다</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>김아영 (지은이)</t>
+          <t>장예원 (지은이)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>19800</v>
+        <v>22000</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>9791193937563</t>
+          <t>9791193937365</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=361151650</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=361643111</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI 패권 전쟁</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>챗GPT 딥시크의 미래와 AI 그 이후</t>
-        </is>
-      </c>
+          <t>모든 걸음에는 이유가 있다</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>이시한 (지은이)</t>
+          <t>김아영 (지은이)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3520,42 +3520,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>22000</v>
+        <v>19800</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>9791193937549</t>
+          <t>9791193937563</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=357398970</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=361151650</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>스위트 스팟</t>
+          <t>AI 패권 전쟁</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>인생의 숨은 기회를 찾는 9가지 통찰</t>
+          <t>챗GPT 딥시크의 미래와 AI 그 이후</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>샘 리처드 (지은이), 김수민 (옮긴이)</t>
+          <t>이시한 (지은이)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3565,42 +3565,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>19800</v>
+        <v>22000</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>9791193937532</t>
+          <t>9791193937549</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=358119007</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=357398970</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>성난 파도 다스리기</t>
+          <t>스위트 스팟</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>소란한 마음을 고요하게 하는 365가지 삶의 지혜</t>
+          <t>인생의 숨은 기회를 찾는 9가지 통찰</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>덩 밍다오 (지은이), 김희균 (옮긴이)</t>
+          <t>샘 리처드 (지은이), 김수민 (옮긴이)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3610,53 +3610,57 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>22000</v>
+        <v>19800</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>9791193937433</t>
+          <t>9791193937532</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=355338819</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=358119007</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>내가 원하는 것을 나도 모를 때</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
+          <t>성난 파도 다스리기</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>소란한 마음을 고요하게 하는 365가지 삶의 지혜</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>전승환 (지은이)</t>
+          <t>덩 밍다오 (지은이), 김희균 (옮긴이)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -3664,44 +3668,40 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>9791193937150</t>
+          <t>9791193937433</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=354981569</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=355338819</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>왜 그들만 부자가 되는가</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>부의 격차를 좁히는 진짜 돈의 모습</t>
-        </is>
-      </c>
+          <t>내가 원하는 것을 나도 모를 때</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>필립 바구스, 안드레아스 마르크바르트 (지은이), 배진아 (옮긴이)</t>
+          <t>전승환 (지은이)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -3709,84 +3709,84 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>9791193937396</t>
+          <t>9791193937150</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=354574933</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=354981569</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>새들이 남쪽으로 가는 날</t>
+          <t>왜 그들만 부자가 되는가</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024 스웨덴 올해의 도서상 수상작</t>
+          <t>부의 격차를 좁히는 진짜 돈의 모습</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>리사 리드센 (지은이), 손화수 (옮긴이)</t>
+          <t>필립 바구스, 안드레아스 마르크바르트 (지은이), 배진아 (옮긴이)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>19500</v>
+        <v>22000</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>9791193937372</t>
+          <t>9791193937396</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=352764746</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=354574933</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>삶의 태도</t>
+          <t>새들이 남쪽으로 가는 날</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>흔들림 없이 나아가는</t>
+          <t>2024 스웨덴 올해의 도서상 수상작</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>반건호 (지은이)</t>
+          <t>리사 리드센 (지은이), 손화수 (옮긴이)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3795,213 +3795,213 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>22000</v>
+        <v>19500</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>9791193937402</t>
+          <t>9791193937372</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=353472576</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=352764746</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>인생을 자유롭게 하는 것들</t>
+          <t>삶의 태도</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>가슴 뛰는 삶을 향해 가는 최우선의 행복</t>
+          <t>흔들림 없이 나아가는</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>나용민, 유숙현 (지은이)</t>
+          <t>반건호 (지은이)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>18000</v>
+        <v>22000</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>9791193937389</t>
+          <t>9791193937402</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=353117247</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=353472576</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>쉼과 나아감에 대하여</t>
+          <t>인생을 자유롭게 하는 것들</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>인생의 오아시스를 만나는 예일대 명강의</t>
+          <t>가슴 뛰는 삶을 향해 가는 최우선의 행복</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>마릴린 폴 (지은이), 김태훈 (옮긴이)</t>
+          <t>나용민, 유숙현 (지은이)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>19800</v>
+        <v>18000</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>9791193937341</t>
+          <t>9791193937389</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=351959853</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=353117247</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>영국 아빠 피터의 하루 3분 영어 대화 (스프링)</t>
+          <t>쉼과 나아감에 대하여</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>스스로 말하고 표현하는 영어 회화 일력</t>
+          <t>인생의 오아시스를 만나는 예일대 명강의</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>피터 빈트 (지은이)</t>
+          <t>마릴린 폴 (지은이), 김태훈 (옮긴이)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>북크레용</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>자녀교육</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>25000</v>
+        <v>19800</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>9791193937280</t>
+          <t>9791193937341</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=350405920</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=351959853</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>질투라는 감옥</t>
+          <t>영국 아빠 피터의 하루 3분 영어 대화 (스프링)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>우리는 왜 타인에게 휘둘리는가</t>
+          <t>스스로 말하고 표현하는 영어 회화 일력</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>야마모토 케이 (지은이), 최주연 (옮긴이)</t>
+          <t>피터 빈트 (지은이)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북크레용</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>자녀교육</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>19800</v>
+        <v>25000</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>9791193937259</t>
+          <t>9791193937280</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=348985847</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=350405920</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>머니 트렌드 2025</t>
+          <t>질투라는 감옥</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>새로운 부의 기회를 선점할 55가지 성공 시나리오</t>
+          <t>우리는 왜 타인에게 휘둘리는가</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>정태익, 김도윤, 김광석, 김용섭, 김현준, 정수종, 채상욱, 최재붕 (지은이)</t>
+          <t>야마모토 케이 (지은이), 최주연 (옮긴이)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4011,143 +4011,147 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>25000</v>
+        <v>19800</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>9791193937211</t>
+          <t>9791193937259</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=345965820</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=348985847</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>마음이 부자인 아이는 어떻게 성장하는가</t>
+          <t>머니 트렌드 2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>행복할 줄 아는 아이로 키우는 정서 육아법</t>
+          <t>새로운 부의 기회를 선점할 55가지 성공 시나리오</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>박소영 (지은이)</t>
+          <t>정태익, 김도윤, 김광석, 김용섭, 김현준, 정수종, 채상욱, 최재붕 (지은이)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>북크레용</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>자녀교육</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>19800</v>
+        <v>25000</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>9791193937228</t>
+          <t>9791193937211</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=346892914</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=345965820</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>엄마에게 안부를 묻는 밤</t>
+          <t>마음이 부자인 아이는 어떻게 성장하는가</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>언제나 내 편인 이 세상 단 한 사람</t>
+          <t>행복할 줄 아는 아이로 키우는 정서 육아법</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>박애희 (지은이)</t>
+          <t>박소영 (지은이)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북크레용</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자녀교육</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>18800</v>
+        <v>19800</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>9791193937242</t>
+          <t>9791193937228</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=346467345</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=346892914</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>빛이 이끄는 곳으로</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>엄마에게 안부를 묻는 밤</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>언제나 내 편인 이 세상 단 한 사람</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>백희성 (지은이)</t>
+          <t>박애희 (지은이)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -4155,29 +4159,25 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>9791193937198</t>
+          <t>9791193937242</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=344497704</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=346467345</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>호감의 시작 (트윙클 에디션)</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>관계, 일, 인생이 풀리는 매력의 법칙</t>
-        </is>
-      </c>
+          <t>빛이 이끄는 곳으로</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>희렌최 (지은이)</t>
+          <t>백희성 (지은이)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4187,47 +4187,47 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>18500</v>
+        <v>18800</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>9791193937143</t>
+          <t>9791193937198</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=342932323</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=344497704</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>나는 도대체 왜 피곤할까</t>
+          <t>호감의 시작 (트윙클 에디션)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>이 죽일 놈의 피로와 결별하는 법</t>
+          <t>관계, 일, 인생이 풀리는 매력의 법칙</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>에이미 샤 (지은이), 김잔디 (옮긴이)</t>
+          <t>희렌최 (지은이)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4237,33 +4237,37 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>19800</v>
+        <v>18500</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>9791193937136</t>
+          <t>9791193937143</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=342083093</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=342932323</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>그럼에도 불구하고 나는 내가 좋았어</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>나는 도대체 왜 피곤할까</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>이 죽일 놈의 피로와 결별하는 법</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>박채린 (지은이)</t>
+          <t>에이미 샤 (지은이), 김잔디 (옮긴이)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4273,102 +4277,98 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>18000</v>
+        <v>19800</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>9791193937105</t>
+          <t>9791193937136</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=340511549</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=342083093</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>부자의 마지막 가르침 (30만 부 리커버)</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>삶의 자유를 위한 부의 알고리즘</t>
-        </is>
-      </c>
+          <t>그럼에도 불구하고 나는 내가 좋았어</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>다우치 마나부 (지은이), 김슬기 (옮긴이)</t>
+          <t>박채린 (지은이)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>19800</v>
+        <v>18000</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>9791193937068</t>
+          <t>9791193937105</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363272157</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=340511549</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>똑똑한 아이는 어떻게 생각하고 질문하는가</t>
+          <t>부자의 마지막 가르침 (30만 부 리커버)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>사고력 실종의 시대, 주도적인 아이들의 생존 전략</t>
+          <t>삶의 자유를 위한 부의 알고리즘</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>이시한 (지은이)</t>
+          <t>다우치 마나부 (지은이), 김슬기 (옮긴이)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>북크레용</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>자녀교육</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -4376,89 +4376,89 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>9791193937037</t>
+          <t>9791193937068</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=337128010</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363272157</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>사랑받는 이기주의자</t>
+          <t>똑똑한 아이는 어떻게 생각하고 질문하는가</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>나를 지키며 사랑받는 관계의 기술</t>
+          <t>사고력 실종의 시대, 주도적인 아이들의 생존 전략</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>박코 (지은이)</t>
+          <t>이시한 (지은이)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북크레용</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>자녀교육</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>18000</v>
+        <v>19800</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>9791193937051</t>
+          <t>9791193937037</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=338458067</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=337128010</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>내가 천 개의 인생에서 배운 것들</t>
+          <t>사랑받는 이기주의자</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>돈, 명예, 시간 그 무엇보다 소중한 것에 관하여</t>
+          <t>나를 지키며 사랑받는 관계의 기술</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>김도윤 (지은이)</t>
+          <t>박코 (지은이)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -4466,79 +4466,79 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>9791198530394</t>
+          <t>9791193937051</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=337269711</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=338458067</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>양수인간</t>
+          <t>내가 천 개의 인생에서 배운 것들</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>삶의 격을 높이는 내면 변화 심리학</t>
+          <t>돈, 명예, 시간 그 무엇보다 소중한 것에 관하여</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>최설민 (지은이)</t>
+          <t>김도윤 (지은이)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>19800</v>
+        <v>18000</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>9791193937006</t>
+          <t>9791198530394</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=336173615</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=337269711</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>무엇이 나를 행복하게 만드는가</t>
+          <t>양수인간</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>인생의 절반쯤 왔을 때 깨닫게 되는 것들</t>
+          <t>삶의 격을 높이는 내면 변화 심리학</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>리처드 J. 라이더, 데이비드 A. 샤피로 (지은이), 김정홍 (옮긴이)</t>
+          <t>최설민 (지은이)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -4556,29 +4556,29 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>9791198530356</t>
+          <t>9791193937006</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=334885758</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=336173615</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>노인의 꿈 : 첫 번째 이야기</t>
+          <t>무엇이 나를 행복하게 만드는가</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>황혼을 향해 걷는 우리 모두의 이야기</t>
+          <t>인생의 절반쯤 왔을 때 깨닫게 되는 것들</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>백원달 (지은이)</t>
+          <t>리처드 J. 라이더, 데이비드 A. 샤피로 (지은이), 김정홍 (옮긴이)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4588,32 +4588,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>그 밖의 책</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>23000</v>
+        <v>19800</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>9791191891478</t>
+          <t>9791198530356</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=335184922</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=334885758</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>노인의 꿈 : 두 번째 이야기</t>
+          <t>노인의 꿈 : 첫 번째 이야기</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4646,29 +4646,29 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>9791191891485</t>
+          <t>9791191891478</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=335185323</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=335184922</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>똑똑한 사람은 어떻게 생각하고 질문하는가</t>
+          <t>노인의 꿈 : 두 번째 이야기</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>사고력 실종의 시대, 앞서가는 사람들의 생존 전략</t>
+          <t>황혼을 향해 걷는 우리 모두의 이야기</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>이시한 (지은이)</t>
+          <t>백원달 (지은이)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4678,42 +4678,42 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>그 밖의 책</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>19800</v>
+        <v>23000</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>9791191891492</t>
+          <t>9791191891485</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=332269449</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=335185323</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>산책하듯 가볍게 (풀빛 에디션)</t>
+          <t>똑똑한 사람은 어떻게 생각하고 질문하는가</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>인생에서 여유를 찾는 당신에게 건네는 말</t>
+          <t>사고력 실종의 시대, 앞서가는 사람들의 생존 전략</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>정우성 (지은이)</t>
+          <t>이시한 (지은이)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4723,47 +4723,47 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>17500</v>
+        <v>19800</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>9791191891447</t>
+          <t>9791191891492</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=388109982</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=332269449</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>하는 일마다 잘되리라</t>
+          <t>산책하듯 가볍게 (풀빛 에디션)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>당신이 어디에 있든 무엇을 하든</t>
+          <t>인생에서 여유를 찾는 당신에게 건네는 말</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>전승환 (지은이)</t>
+          <t>정우성 (지은이)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4773,127 +4773,127 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>18000</v>
+        <v>17500</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>9791198530301</t>
+          <t>9791191891447</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=328632910</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=388109982</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>머니 트렌드 2024</t>
+          <t>하는 일마다 잘되리라</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>57가지 키워드로 전망하는 대한민국 돈의 흐름</t>
+          <t>당신이 어디에 있든 무엇을 하든</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>김도윤, 정태익, 김용섭, 김현준, 전영수, 채상욱, 최재붕, 홍춘욱 (지은이)</t>
+          <t>전승환 (지은이)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>25000</v>
+        <v>18000</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>9791191891416</t>
+          <t>9791198530301</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=324498127</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=328632910</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>꽃은 누구에게나 핀다</t>
+          <t>머니 트렌드 2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>오늘부터 내 삶을 바꾸는 자기 확신 에세이, 매일 더 설레는 날을 살게 될 당신에</t>
+          <t>57가지 키워드로 전망하는 대한민국 돈의 흐름</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>오은환 (지은이)</t>
+          <t>김도윤, 정태익, 김용섭, 김현준, 전영수, 채상욱, 최재붕, 홍춘욱 (지은이)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>17500</v>
+        <v>25000</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>9791191891409</t>
+          <t>9791191891416</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=324723810</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=324498127</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>나는 너랑 노는 게 제일 좋아</t>
+          <t>꽃은 누구에게나 핀다</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>아끼고 고맙고 사랑하는 당신에게</t>
+          <t>오늘부터 내 삶을 바꾸는 자기 확신 에세이, 매일 더 설레는 날을 살게 될 당신에</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>하태완 (지은이)</t>
+          <t>오은환 (지은이)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -4916,29 +4916,29 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>9791191891362</t>
+          <t>9791191891409</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=320503944</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=324723810</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>마음의 자유</t>
+          <t>나는 너랑 노는 게 제일 좋아</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>행복이란 마음이 어디에도 얽매이지 않는 것</t>
+          <t>아끼고 고맙고 사랑하는 당신에게</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>정윤 (지은이)</t>
+          <t>하태완 (지은이)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4953,37 +4953,37 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>17000</v>
+        <v>17500</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>9791191891355</t>
+          <t>9791191891362</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=318438169</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=320503944</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>찌그러져도 괜찮아</t>
+          <t>마음의 자유</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>이미 찌그러진 오리가</t>
+          <t>행복이란 마음이 어디에도 얽매이지 않는 것</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>찌오(임임) (지은이)</t>
+          <t>정윤 (지은이)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -5006,35 +5006,39 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>9791191891324</t>
+          <t>9791191891355</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=315987317</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=318438169</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>인생에서 가장 후회되는 게 뭐냐고 묻는다면</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+          <t>찌그러져도 괜찮아</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>이미 찌그러진 오리가</t>
+        </is>
+      </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>노우티 (지은이)</t>
+          <t>찌오(임임) (지은이)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5043,156 +5047,156 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>17500</v>
+        <v>17000</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>9791191891331</t>
+          <t>9791191891324</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=315418702</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=315987317</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>당신과 아침에 싸우면 밤에는 입맞출 겁니다</t>
+          <t>인생에서 가장 후회되는 게 뭐냐고 묻는다면</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>유래혁 (지은이)</t>
+          <t>노우티 (지은이)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>17000</v>
+        <v>17500</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>9791191891263</t>
+          <t>9791191891331</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=313695065</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=315418702</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GPT 제너레이션 : 챗GPT가 바꿀 우리 인류의 미래</t>
+          <t>당신과 아침에 싸우면 밤에는 입맞출 겁니다</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>이시한 (지은이)</t>
+          <t>유래혁 (지은이)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>19000</v>
+        <v>17000</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>9791191891270</t>
+          <t>9791191891263</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=310813322</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=313695065</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>오둥이입니다만!</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>나는 세상에서 가장 행복한 오리</t>
-        </is>
-      </c>
+          <t>GPT 제너레이션 : 챗GPT가 바꿀 우리 인류의 미래</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>송 스튜디오 (지은이)</t>
+          <t>이시한 (지은이)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>17000</v>
+        <v>19000</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>9791191891256</t>
+          <t>9791191891270</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=310407734</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=310813322</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>행복을 담아줄게</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
+          <t>오둥이입니다만!</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>나는 세상에서 가장 행복한 오리</t>
+        </is>
+      </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>나란 (지은이)</t>
+          <t>송 스튜디오 (지은이)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5207,37 +5211,33 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>16000</v>
+        <v>17000</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>9791191891249</t>
+          <t>9791191891256</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=309568882</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=310407734</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>나는 오늘의 내가 좋아</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>긍정토끼 몰랑이의 몰랑몰랑 마음 일기</t>
-        </is>
-      </c>
+          <t>행복을 담아줄게</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>윤혜지(하얀오리) (지은이)</t>
+          <t>나란 (지은이)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2023-01-30</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -5260,111 +5260,115 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>9791191891126</t>
+          <t>9791191891249</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=306216745</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=309568882</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>머니 트렌드 2023</t>
+          <t>나는 오늘의 내가 좋아</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>45가지 키워드로 전망하는 대한민국 돈의 흐름</t>
+          <t>긍정토끼 몰랑이의 몰랑몰랑 마음 일기</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>부동산읽어주는남자(정태익), 김도윤, 김경민, 김상균, 전영수, 최준철, 홍춘욱 (지은이)</t>
+          <t>윤혜지(하얀오리) (지은이)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>19000</v>
+        <v>16000</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>9791191891232</t>
+          <t>9791191891126</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=304588805</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=306216745</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>잘될 수밖에 없는 너에게</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>머니 트렌드 2023</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>45가지 키워드로 전망하는 대한민국 돈의 흐름</t>
+        </is>
+      </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>최서영 (지은이)</t>
+          <t>부동산읽어주는남자(정태익), 김도윤, 김경민, 김상균, 전영수, 최준철, 홍춘욱 (지은이)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>19500</v>
+        <v>19000</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>9791191891201</t>
+          <t>9791191891232</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=299808248</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=304588805</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>나로서 충분히 괜찮은 사람</t>
+          <t>잘될 수밖에 없는 너에게</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>김재식 (지은이)</t>
+          <t>최서영 (지은이)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5379,37 +5383,33 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>16000</v>
+        <v>19500</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>9791191891096</t>
+          <t>9791191891201</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=294392417</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=299808248</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>나에게 고맙다</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>30만 부 기념 전면개정판</t>
-        </is>
-      </c>
+          <t>나로서 충분히 괜찮은 사람</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>전승환 (지은이)</t>
+          <t>김재식 (지은이)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5424,37 +5424,37 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>2022-05-10</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>19000</v>
+        <v>16000</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>9791191891072</t>
+          <t>9791191891096</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=289269041</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=294392417</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>럭키 LUCKY</t>
+          <t>나에게 고맙다</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>내 안에 잠든 운을 깨우는 7가지 법칙</t>
+          <t>30만 부 기념 전면개정판</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>김도윤 (지은이)</t>
+          <t>전승환 (지은이)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5464,42 +5464,42 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>9791191891027</t>
+          <t>9791191891072</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=278177114</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=289269041</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>그렇다면 나를 응원할 수밖에 (윈터 에디션)</t>
+          <t>럭키 LUCKY</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>멋대로지만 제대로 사는 중입니다</t>
+          <t>내 안에 잠든 운을 깨우는 7가지 법칙</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>김수민 (지은이)</t>
+          <t>김도윤 (지은이)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5509,38 +5509,42 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
+          <t>2021-08-25</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>9791197037191</t>
+          <t>9791191891027</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=283440909</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=278177114</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>작은 별이지만 빛나고 있어 (30만부 기념 미드나잇 에디션)</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>그렇다면 나를 응원할 수밖에 (윈터 에디션)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>멋대로지만 제대로 사는 중입니다</t>
+        </is>
+      </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>소윤 (지은이)</t>
+          <t>김수민 (지은이)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5555,33 +5559,33 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>19000</v>
+        <v>15000</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>9791197037153</t>
+          <t>9791197037191</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=367659804</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=283440909</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>좋은 건 같이 봐요</t>
+          <t>작은 별이지만 빛나고 있어 (30만부 기념 미드나잇 에디션)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>엄지사진관 (지은이)</t>
+          <t>소윤 (지은이)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5596,33 +5600,33 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2021-01-27</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>15000</v>
+        <v>19000</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>9791197037146</t>
+          <t>9791197037153</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=262375795</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=367659804</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>안녕, 소중한 사람</t>
+          <t>좋은 건 같이 봐요</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>정한경 (지은이)</t>
+          <t>엄지사진관 (지은이)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5637,63 +5641,104 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2021-01-27</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>19000</v>
+        <v>15000</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>9791197037122</t>
+          <t>9791197037146</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=251524184</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=262375795</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>안녕, 소중한 사람</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>정한경 (지은이)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>북로망스</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>에세이</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>19000</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>9791197037122</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=251524184</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
           <t>나는 나를 사랑한다</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>나를 잃지 않고 타인을 사랑하기 위하여</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>이숙명 (지은이)</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>북로망스</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>에세이</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>2020-06-24</t>
         </is>
       </c>
-      <c r="G121" t="n">
+      <c r="G122" t="n">
         <v>14800</v>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>9791197037108</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="I122" t="inlineStr">
         <is>
           <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=242494208</t>
         </is>
@@ -5710,7 +5755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5766,39 +5811,31 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A Briefing on Knowledge for Conversations Worth Having (Special Limited Edition)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>The knowledge behind thoughtful, well-informed conversation.</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>품격 있는 대화를 위한 지식 브리핑 (10만 부 기념 특별 한정판)</t>
+          <t>나답게 똘똘하게</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>김진</t>
+          <t>김똘똘(김반석)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>9791124038413</t>
+          <t>9791124038956</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5810,37 +5847,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Money Trend 2027</t>
+          <t>A Briefing on Knowledge for Conversations Worth Having (Special Limited Edition)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>55 currents of money that turn upheaval into opportunity.</t>
+          <t>The knowledge behind thoughtful, well-informed conversation.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>머니 트렌드 2027</t>
+          <t>품격 있는 대화를 위한 지식 브리핑 (10만 부 기념 특별 한정판)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>정태익, 김도윤, 김광석, 김용섭, 김학렬, 박세익, 박정호, 이효석</t>
+          <t>김진</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9791124038826</t>
+          <t>9791124038413</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5852,27 +5889,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Meeting Philosophy for the First Time</t>
+          <t>Money Trend 2027</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The moment philosophy walks into your life.</t>
+          <t>55 currents of money that turn upheaval into opportunity.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>처음 만나는 철학의 세계</t>
+          <t>머니 트렌드 2027</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>성창원</t>
+          <t>정태익, 김도윤, 김광석, 김용섭, 김학렬, 박세익, 박정호, 이효석</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5882,7 +5919,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9791124038833</t>
+          <t>9791124038826</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5894,37 +5931,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>How Smart People Talk</t>
+          <t>Meeting Philosophy for the First Time</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Speaking strategies of people who earn trust without talking long.</t>
+          <t>The moment philosophy walks into your life.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>똑똑한 사람은 어떻게 말하는가</t>
+          <t>처음 만나는 철학의 세계</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>이시한</t>
+          <t>성창원</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9791124038642</t>
+          <t>9791124038833</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5936,37 +5973,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>The Texture of Memory</t>
+          <t>How Smart People Talk</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unable to recognize faces, she reads people through cloth and gait.</t>
+          <t>Speaking strategies of people who earn trust without talking long.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>기억의 무늬</t>
+          <t>똑똑한 사람은 어떻게 말하는가</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>백희성</t>
+          <t>이시한</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9791124038604</t>
+          <t>9791124038642</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5978,37 +6015,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Your Happiness Is My Joy</t>
+          <t>The Texture of Memory</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>To love someone is to find your joy in theirs.</t>
+          <t>Unable to recognize faces, she reads people through cloth and gait.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>너의 행복은 나의 기쁨이야</t>
+          <t>기억의 무늬</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>정한경</t>
+          <t>백희성</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>9791124038574</t>
+          <t>9791124038604</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -6020,37 +6057,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>The Secret of Magnetic People</t>
+          <t>Your Happiness Is My Joy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Graceful words and bearing that move hearts.</t>
+          <t>To love someone is to find your joy in theirs.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>끌리는 사람의 비밀</t>
+          <t>너의 행복은 나의 기쁨이야</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>조수빈</t>
+          <t>정한경</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9791124038567</t>
+          <t>9791124038574</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -6062,37 +6099,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>The Double-Decker Bus of Richmond Hill</t>
+          <t>The Secret of Magnetic People</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>If you could change the past, would you choose differently?</t>
+          <t>Graceful words and bearing that move hearts.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>리치먼드힐의 이층 버스</t>
+          <t>끌리는 사람의 비밀</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>이경진</t>
+          <t>조수빈</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9791124038499</t>
+          <t>9791124038567</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -6104,37 +6141,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>The Original Code</t>
+          <t>The Double-Decker Bus of Richmond Hill</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Work like yourself, succeed like yourself.</t>
+          <t>If you could change the past, would you choose differently?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>오리지널 코드</t>
+          <t>리치먼드힐의 이층 버스</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>오은환</t>
+          <t>이경진</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9791124038369</t>
+          <t>9791124038499</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -6146,37 +6183,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>My Perfect Funeral</t>
+          <t>The Original Code</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Warm hope, found between life and death.</t>
+          <t>Work like yourself, succeed like yourself.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>나의 완벽한 장례식</t>
+          <t>오리지널 코드</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>조현선</t>
+          <t>오은환</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9791124038192</t>
+          <t>9791124038369</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -6188,37 +6225,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Callie's Routine English</t>
+          <t>My Perfect Funeral</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10 minutes a day, 90 days, one lasting English habit.</t>
+          <t>Warm hope, found between life and death.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>캘리쌤의 루틴 잉글리시</t>
+          <t>나의 완벽한 장례식</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>캘리쌤</t>
+          <t>조현선</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9791124038123</t>
+          <t>9791124038192</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -6230,37 +6267,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mileage Hours</t>
+          <t>Callie's Routine English</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The art of designing a life of greater quality.</t>
+          <t>10 minutes a day, 90 days, one lasting English habit.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>마일리지 아워</t>
+          <t>캘리쌤의 루틴 잉글리시</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>최유나</t>
+          <t>캘리쌤</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9791124038093</t>
+          <t>9791124038123</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -6272,37 +6309,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>The Dignity of Adulthood</t>
+          <t>Mileage Hours</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The life attitudes that make a real grown-up.</t>
+          <t>The art of designing a life of greater quality.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>어른의 품위</t>
+          <t>마일리지 아워</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>최서영</t>
+          <t>최유나</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9791193937693</t>
+          <t>9791124038093</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -6314,37 +6351,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Money Trend 2026</t>
+          <t>The Dignity of Adulthood</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50 survival formulas for the flow of money in uncertain times.</t>
+          <t>The life attitudes that make a real grown-up.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>머니 트렌드 2026</t>
+          <t>어른의 품위</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>김도윤, 정태익, 김광석, 김승주, 김용섭, 김학렬(빠숑), 김현준, 최재붕</t>
+          <t>최서영</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9791193937686</t>
+          <t>9791193937693</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -6356,37 +6393,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Meeting the Quantum World for the First Time</t>
+          <t>Money Trend 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>From quantum mechanics to quantum computers.</t>
+          <t>50 survival formulas for the flow of money in uncertain times.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>처음 만나는 양자의 세계</t>
+          <t>머니 트렌드 2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>채은미</t>
+          <t>김도윤, 정태익, 김광석, 김승주, 김용섭, 김학렬(빠숑), 김현준, 최재붕</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9791193937990</t>
+          <t>9791193937686</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -6398,22 +6435,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Knowledge Beyond the Gaze</t>
+          <t>Meeting the Quantum World for the First Time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nine questions that reveal hidden worlds.</t>
+          <t>From quantum mechanics to quantum computers.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>시선 너머의 지식</t>
+          <t>처음 만나는 양자의 세계</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>윤수용</t>
+          <t>채은미</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6423,12 +6460,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>9791193937785</t>
+          <t>9791193937990</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -6440,37 +6477,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>The Marigold Atelier Collection (Limited Edition Box Set)</t>
+          <t>Knowledge Beyond the Gaze</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The complete, internationally acclaimed Marigold trilogy in one set.</t>
+          <t>Nine questions that reveal hidden worlds.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>메리골드 아틀리에 컬렉션 특별 한정판 세트</t>
+          <t>시선 너머의 지식</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>윤정은</t>
+          <t>윤수용</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>9791193937754</t>
+          <t>9791193937785</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6482,17 +6519,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marigold Mind Garden (Atelier Collection)</t>
+          <t>The Marigold Atelier Collection (Limited Edition Box Set)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>What if unhealed wounds could bloom into flowers and trees?</t>
+          <t>The complete, internationally acclaimed Marigold trilogy in one set.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>메리골드 마음 식물원 (아틀리에 컬렉션)</t>
+          <t>메리골드 아틀리에 컬렉션 특별 한정판 세트</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6512,7 +6549,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9791193937723</t>
+          <t>9791193937754</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6524,17 +6561,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marigold Mind Photo Studio (Atelier Collection)</t>
+          <t>Marigold Mind Garden (Atelier Collection)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The second Marigold story, more delicate and thoughtful than the first.</t>
+          <t>What if unhealed wounds could bloom into flowers and trees?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>메리골드 마음 사진관 (아틀리에 컬렉션)</t>
+          <t>메리골드 마음 식물원 (아틀리에 컬렉션)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6554,7 +6591,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>9791193937730</t>
+          <t>9791193937723</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6566,17 +6603,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marigold Mind Laundry (Atelier Collection)</t>
+          <t>Marigold Mind Photo Studio (Atelier Collection)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A beloved K-healing fantasy returns in a special edition.</t>
+          <t>The second Marigold story, more delicate and thoughtful than the first.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>메리골드 마음 세탁소 (아틀리에 컬렉션)</t>
+          <t>메리골드 마음 사진관 (아틀리에 컬렉션)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6596,7 +6633,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>9791193937310</t>
+          <t>9791193937730</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6608,37 +6645,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Meet Me in Our Paradise</t>
+          <t>Marigold Mind Laundry (Atelier Collection)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>For you, crossing this season together with me.</t>
+          <t>A beloved K-healing fantasy returns in a special edition.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>우리의 낙원에서 만나자</t>
+          <t>메리골드 마음 세탁소 (아틀리에 컬렉션)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>하태완</t>
+          <t>윤정은</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>9791193937655</t>
+          <t>9791193937310</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6650,37 +6687,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Core Thinking</t>
+          <t>Meet Me in Our Paradise</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The art of thinking that cuts to the essence of work.</t>
+          <t>For you, crossing this season together with me.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>코어 씽킹 Core Thinking</t>
+          <t>우리의 낙원에서 만나자</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>김범섭</t>
+          <t>하태완</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>9791193937624</t>
+          <t>9791193937655</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6692,37 +6729,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>You Are Always Okay</t>
+          <t>Core Thinking</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>How to steady yourself and stand firm after a shaky time.</t>
+          <t>The art of thinking that cuts to the essence of work.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>당신은 언제나 괜찮다</t>
+          <t>코어 씽킹 Core Thinking</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>이현수</t>
+          <t>김범섭</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>9791193937617</t>
+          <t>9791193937624</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6734,37 +6771,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Everything Will Be Alright, Until Happiness Overflows</t>
+          <t>You Are Always Okay</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gentle words for the feelings we never managed to say out loud.</t>
+          <t>How to steady yourself and stand firm after a shaky time.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>다 좋아질 거야, 행복이 쏟아질 만큼</t>
+          <t>당신은 언제나 괜찮다</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>길연우</t>
+          <t>이현수</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>9791193937594</t>
+          <t>9791193937617</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -6776,37 +6813,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Time to Write Myself</t>
+          <t>Everything Will Be Alright, Until Happiness Overflows</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>One line a day can change a life.</t>
+          <t>Gentle words for the feelings we never managed to say out loud.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>나를 쓰는 시간</t>
+          <t>다 좋아질 거야, 행복이 쏟아질 만큼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>장예원</t>
+          <t>길연우</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>9791193937365</t>
+          <t>9791193937594</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -6818,37 +6855,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Every Step Has Its Reason</t>
+          <t>Time to Write Myself</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A former TV reporter's journey toward happiness, offered as a map.</t>
+          <t>One line a day can change a life.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>모든 걸음에는 이유가 있다</t>
+          <t>나를 쓰는 시간</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>김아영</t>
+          <t>장예원</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>9791193937563</t>
+          <t>9791193937365</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -6860,37 +6897,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>The AI Supremacy War: ChatGPT, DeepSeek, and What Comes Next</t>
+          <t>Every Step Has Its Reason</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Make the AI era your weapon instead of falling behind.</t>
+          <t>A former TV reporter's journey toward happiness, offered as a map.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AI 패권 전쟁</t>
+          <t>모든 걸음에는 이유가 있다</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>이시한</t>
+          <t>김아영</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>9791193937549</t>
+          <t>9791193937563</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -6902,37 +6939,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>When You Don't Know What You Want</t>
+          <t>The AI Supremacy War: ChatGPT, DeepSeek, and What Comes Next</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>150 lines from literature and philosophy to find your way again.</t>
+          <t>Make the AI era your weapon instead of falling behind.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>내가 원하는 것을 나도 모를 때</t>
+          <t>AI 패권 전쟁</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>전승환</t>
+          <t>이시한</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>9791193937150</t>
+          <t>9791193937549</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -6944,22 +6981,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Attitude Toward Life: Moving Forward Without Wavering</t>
+          <t>When You Don't Know What You Want</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Can people really change, and what changes them?</t>
+          <t>150 lines from literature and philosophy to find your way again.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>삶의 태도</t>
+          <t>내가 원하는 것을 나도 모를 때</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>반건호</t>
+          <t>전승환</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6969,12 +7006,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>9791193937402</t>
+          <t>9791193937150</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6986,37 +7023,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>The Things That Set a Life Free</t>
+          <t>Attitude Toward Life: Moving Forward Without Wavering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Putting the happiness that makes your heart race first.</t>
+          <t>Can people really change, and what changes them?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>인생을 자유롭게 하는 것들</t>
+          <t>삶의 태도</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>나용민, 유숙현</t>
+          <t>반건호</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>9791193937389</t>
+          <t>9791193937402</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -7028,37 +7065,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>British Dad Peter's 3-Minute Daily English Conversations (Spring-Bound Daily Calendar)</t>
+          <t>The Things That Set a Life Free</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A flip calendar that gets parents and kids talking in English daily.</t>
+          <t>Putting the happiness that makes your heart race first.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>영국 아빠 피터의 하루 3분 영어 대화 (스프링)</t>
+          <t>인생을 자유롭게 하는 것들</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>피터 빈트</t>
+          <t>나용민, 유숙현</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Parenting</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>9791193937280</t>
+          <t>9791193937389</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -7070,37 +7107,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Money Trend 2025</t>
+          <t>British Dad Peter's 3-Minute Daily English Conversations (Spring-Bound Daily Calendar)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>55 scenarios for seizing the next opportunities in wealth.</t>
+          <t>A flip calendar that gets parents and kids talking in English daily.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>머니 트렌드 2025</t>
+          <t>영국 아빠 피터의 하루 3분 영어 대화 (스프링)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>정태익, 김도윤, 김광석, 김용섭, 김현준, 정수종, 채상욱, 최재붕</t>
+          <t>피터 빈트</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Parenting</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>9791193937211</t>
+          <t>9791193937280</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -7112,37 +7149,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>How Emotionally Rich Children Grow</t>
+          <t>Money Trend 2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>An emotion-centered approach to raising children who know how to be happy.</t>
+          <t>55 scenarios for seizing the next opportunities in wealth.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>마음이 부자인 아이는 어떻게 성장하는가</t>
+          <t>머니 트렌드 2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>박소영</t>
+          <t>정태익, 김도윤, 김광석, 김용섭, 김현준, 정수종, 채상욱, 최재붕</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Parenting</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>9791193937228</t>
+          <t>9791193937211</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -7154,37 +7191,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>The Night I Asked After Mom</t>
+          <t>How Emotionally Rich Children Grow</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The one person in the world who is always on your side.</t>
+          <t>An emotion-centered approach to raising children who know how to be happy.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>엄마에게 안부를 묻는 밤</t>
+          <t>마음이 부자인 아이는 어떻게 성장하는가</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>박애희</t>
+          <t>박소영</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Parenting</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>9791193937242</t>
+          <t>9791193937228</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -7196,37 +7233,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Where the Light Leads</t>
+          <t>The Night I Asked After Mom</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A Paris architect is offered a historic mansion and learns why.</t>
+          <t>The one person in the world who is always on your side.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>빛이 이끄는 곳으로</t>
+          <t>엄마에게 안부를 묻는 밤</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>백희성</t>
+          <t>박애희</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>9791193937198</t>
+          <t>9791193937242</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -7238,37 +7275,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>The Art of Likability (Twinkle Edition)</t>
+          <t>Where the Light Leads</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The principles of charm that make relationships, work, and life flow.</t>
+          <t>A Paris architect is offered a historic mansion and learns why.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>호감의 시작 (트윙클 에디션)</t>
+          <t>빛이 이끄는 곳으로</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>희렌최</t>
+          <t>백희성</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9791193937143</t>
+          <t>9791193937198</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -7280,37 +7317,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Even So, I Liked Myself</t>
+          <t>The Art of Likability (Twinkle Edition)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>From a million-subscriber peak to rock bottom, and unexpectedly happier.</t>
+          <t>The principles of charm that make relationships, work, and life flow.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>그럼에도 불구하고 나는 내가 좋았어</t>
+          <t>호감의 시작 (트윙클 에디션)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>박채린</t>
+          <t>희렌최</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>9791193937105</t>
+          <t>9791193937143</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -7322,37 +7359,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>How Smart Kids Think and Ask Questions</t>
+          <t>Even So, I Liked Myself</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Survival strategies for self-driven children in an age of fading thinking skills.</t>
+          <t>From a million-subscriber peak to rock bottom, and unexpectedly happier.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>똑똑한 아이는 어떻게 생각하고 질문하는가</t>
+          <t>그럼에도 불구하고 나는 내가 좋았어</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>이시한</t>
+          <t>박채린</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Parenting</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>9791193937037</t>
+          <t>9791193937105</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -7364,37 +7401,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>The Lovable Egoist</t>
+          <t>How Smart Kids Think and Ask Questions</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The art of protecting yourself and still being loved.</t>
+          <t>Survival strategies for self-driven children in an age of fading thinking skills.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>사랑받는 이기주의자</t>
+          <t>똑똑한 아이는 어떻게 생각하고 질문하는가</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>박코</t>
+          <t>이시한</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Parenting</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>9791193937051</t>
+          <t>9791193937037</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -7406,37 +7443,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>What I Learned from a Thousand Lives</t>
+          <t>The Lovable Egoist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>On what matters more than money, fame, or time.</t>
+          <t>The art of protecting yourself and still being loved.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>내가 천 개의 인생에서 배운 것들</t>
+          <t>사랑받는 이기주의자</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>김도윤</t>
+          <t>박코</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>9791198530394</t>
+          <t>9791193937051</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -7448,37 +7485,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>The Positive-Sum Person</t>
+          <t>What I Learned from a Thousand Lives</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A psychology of inner change that raises the quality of your life.</t>
+          <t>On what matters more than money, fame, or time.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>양수인간</t>
+          <t>내가 천 개의 인생에서 배운 것들</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>최설민</t>
+          <t>김도윤</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>9791193937006</t>
+          <t>9791198530394</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -7490,37 +7527,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>An Elder's Dream, Vol. 1</t>
+          <t>The Positive-Sum Person</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A story for all of us walking toward twilight.</t>
+          <t>A psychology of inner change that raises the quality of your life.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>노인의 꿈 : 첫 번째 이야기</t>
+          <t>양수인간</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>백원달</t>
+          <t>최설민</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>9791191891478</t>
+          <t>9791193937006</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -7532,7 +7569,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>An Elder's Dream, Vol. 2</t>
+          <t>An Elder's Dream, Vol. 1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7542,7 +7579,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>노인의 꿈 : 두 번째 이야기</t>
+          <t>노인의 꿈 : 첫 번째 이야기</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7562,7 +7599,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>9791191891485</t>
+          <t>9791191891478</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7574,37 +7611,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>How Smart People Think and Ask Questions</t>
+          <t>An Elder's Dream, Vol. 2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Survival strategies for staying ahead as thinking skills fade.</t>
+          <t>A story for all of us walking toward twilight.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>똑똑한 사람은 어떻게 생각하고 질문하는가</t>
+          <t>노인의 꿈 : 두 번째 이야기</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>이시한</t>
+          <t>백원달</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>9791191891492</t>
+          <t>9791191891485</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7616,37 +7653,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Take It Easy, Like a Walk (Green Edition)</t>
+          <t>How Smart People Think and Ask Questions</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Words for anyone trying to find some breathing room in life.</t>
+          <t>Survival strategies for staying ahead as thinking skills fade.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>산책하듯 가볍게 (풀빛 에디션)</t>
+          <t>똑똑한 사람은 어떻게 생각하고 질문하는가</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>정우성</t>
+          <t>이시한</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>9791191891447</t>
+          <t>9791191891492</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7658,22 +7695,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>May Everything You Do Go Well</t>
+          <t>Take It Easy, Like a Walk (Green Edition)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Wherever you are, whatever you do, hope is with you.</t>
+          <t>Words for anyone trying to find some breathing room in life.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>하는 일마다 잘되리라</t>
+          <t>산책하듯 가볍게 (풀빛 에디션)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>전승환</t>
+          <t>정우성</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -7683,12 +7720,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>9791198530301</t>
+          <t>9791191891447</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7700,37 +7737,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Money Trend 2024</t>
+          <t>May Everything You Do Go Well</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>57 keywords that map the flow of money in Korea.</t>
+          <t>Wherever you are, whatever you do, hope is with you.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>머니 트렌드 2024</t>
+          <t>하는 일마다 잘되리라</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>김도윤, 정태익, 김용섭, 김현준, 전영수, 채상욱, 최재붕, 홍춘욱</t>
+          <t>전승환</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>9791191891416</t>
+          <t>9791198530301</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7742,37 +7779,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Everyone Blooms</t>
+          <t>Money Trend 2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>A self-belief essay for living every day with more anticipation.</t>
+          <t>57 keywords that map the flow of money in Korea.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>꽃은 누구에게나 핀다</t>
+          <t>머니 트렌드 2024</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>오은환</t>
+          <t>김도윤, 정태익, 김용섭, 김현준, 전영수, 채상욱, 최재붕, 홍춘욱</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>9791191891409</t>
+          <t>9791191891416</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7784,22 +7821,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>I Like Playing with You Best</t>
+          <t>Everyone Blooms</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>For the one you cherish, thank and love.</t>
+          <t>A self-belief essay for living every day with more anticipation.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>나는 너랑 노는 게 제일 좋아</t>
+          <t>꽃은 누구에게나 핀다</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>하태완</t>
+          <t>오은환</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -7809,12 +7846,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>9791191891362</t>
+          <t>9791191891409</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7826,22 +7863,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Freedom of Mind</t>
+          <t>I Like Playing with You Best</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Happiness is a mind that is not bound to anything.</t>
+          <t>For the one you cherish, thank and love.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>마음의 자유</t>
+          <t>나는 너랑 노는 게 제일 좋아</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>정윤</t>
+          <t>하태완</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -7851,12 +7888,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>9791191891355</t>
+          <t>9791191891362</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7868,22 +7905,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>It's Okay to Be Dented</t>
+          <t>Freedom of Mind</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Words from a duck who is already dented.</t>
+          <t>Happiness is a mind that is not bound to anything.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>찌그러져도 괜찮아</t>
+          <t>마음의 자유</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>찌오(임임)</t>
+          <t>정윤</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -7893,12 +7930,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>9791191891324</t>
+          <t>9791191891355</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7910,27 +7947,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>If You Ask What I Regret Most in Life</t>
+          <t>It's Okay to Be Dented</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>"If you could go back, what would you change?"</t>
+          <t>Words from a duck who is already dented.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>인생에서 가장 후회되는 게 뭐냐고 묻는다면</t>
+          <t>찌그러져도 괜찮아</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>노우티</t>
+          <t>찌오(임임)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -7940,7 +7977,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>9791191891331</t>
+          <t>9791191891324</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -7952,37 +7989,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>If We Fight in the Morning, I'll Kiss You at Night</t>
+          <t>If You Ask What I Regret Most in Life</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Every feeling of love, caught in words and photographs.</t>
+          <t>"If you could go back, what would you change?"</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>당신과 아침에 싸우면 밤에는 입맞출 겁니다</t>
+          <t>인생에서 가장 후회되는 게 뭐냐고 묻는다면</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>유래혁</t>
+          <t>노우티</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>9791191891263</t>
+          <t>9791191891331</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7994,37 +8031,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GPT Generation: How ChatGPT Will Change Humanity's Future</t>
+          <t>If We Fight in the Morning, I'll Kiss You at Night</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A mega-trend is only beginning, and it will reshape everyday life.</t>
+          <t>Every feeling of love, caught in words and photographs.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GPT 제너레이션 : 챗GPT가 바꿀 우리 인류의 미래</t>
+          <t>당신과 아침에 싸우면 밤에는 입맞출 겁니다</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>이시한</t>
+          <t>유래혁</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>9791191891270</t>
+          <t>9791191891263</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8036,37 +8073,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>I'm Odungi, Actually!</t>
+          <t>GPT Generation: How ChatGPT Will Change Humanity's Future</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The happiest duck in the world.</t>
+          <t>A mega-trend is only beginning, and it will reshape everyday life.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>오둥이입니다만!</t>
+          <t>GPT 제너레이션 : 챗GPT가 바꿀 우리 인류의 미래</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>송 스튜디오</t>
+          <t>이시한</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>9791191891256</t>
+          <t>9791191891270</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8078,22 +8115,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>I'll Pour Happiness In for You</t>
+          <t>I'm Odungi, Actually!</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gem-like stories to carry your ordinary life to its brightest moments.</t>
+          <t>The happiest duck in the world.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>행복을 담아줄게</t>
+          <t>오둥이입니다만!</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>나란</t>
+          <t>송 스튜디오</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -8103,12 +8140,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>9791191891249</t>
+          <t>9791191891256</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8120,22 +8157,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>I Like Who I Am Today</t>
+          <t>I'll Pour Happiness In for You</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The soft, squishy diary of Molang, the positive rabbit.</t>
+          <t>Gem-like stories to carry your ordinary life to its brightest moments.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>나는 오늘의 내가 좋아</t>
+          <t>행복을 담아줄게</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>윤혜지(하얀오리)</t>
+          <t>나란</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -8145,12 +8182,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2023-01-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>9791191891126</t>
+          <t>9791191891249</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8162,37 +8199,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Money Trend 2023</t>
+          <t>I Like Who I Am Today</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>45 keywords that map the flow of money in Korea.</t>
+          <t>The soft, squishy diary of Molang, the positive rabbit.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>머니 트렌드 2023</t>
+          <t>나는 오늘의 내가 좋아</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>부동산읽어주는남자(정태익), 김도윤, 김경민, 김상균, 전영수, 최준철, 홍춘욱</t>
+          <t>윤혜지(하얀오리)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>9791191891232</t>
+          <t>9791191891126</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8204,37 +8241,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>You're Bound to Do Well</t>
+          <t>Money Trend 2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Practical encouragement for living and working better.</t>
+          <t>45 keywords that map the flow of money in Korea.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>잘될 수밖에 없는 너에게</t>
+          <t>머니 트렌드 2023</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>최서영</t>
+          <t>부동산읽어주는남자(정태익), 김도윤, 김경민, 김상균, 전영수, 최준철, 홍춘욱</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>9791191891201</t>
+          <t>9791191891232</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8246,22 +8283,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Good Enough, Just as I Am</t>
+          <t>You're Bound to Do Well</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A letter of warm empathy and encouragement.</t>
+          <t>Practical encouragement for living and working better.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>나로서 충분히 괜찮은 사람</t>
+          <t>잘될 수밖에 없는 너에게</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>김재식</t>
+          <t>최서영</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -8271,12 +8308,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>9791191891096</t>
+          <t>9791191891201</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8288,22 +8325,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Thank You, Me (Fully Revised Edition)</t>
+          <t>Good Enough, Just as I Am</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>A healing essay collection, fully revised to mark 300,000 copies sold.</t>
+          <t>A letter of warm empathy and encouragement.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>나에게 고맙다</t>
+          <t>나로서 충분히 괜찮은 사람</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>전승환</t>
+          <t>김재식</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -8313,12 +8350,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>2022-05-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>9791191891072</t>
+          <t>9791191891096</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8330,37 +8367,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LUCKY: 7 Rules for Awakening the Luck Within</t>
+          <t>Thank You, Me (Fully Revised Edition)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What 1,000 successful people all said: "I was lucky."</t>
+          <t>A healing essay collection, fully revised to mark 300,000 copies sold.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>럭키 LUCKY</t>
+          <t>나에게 고맙다</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>김도윤</t>
+          <t>전승환</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>9791191891027</t>
+          <t>9791191891072</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8372,37 +8409,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Then I Have No Choice but to Cheer Myself On (Winter Edition)</t>
+          <t>LUCKY: 7 Rules for Awakening the Luck Within</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Doing life my own way, and doing it right.</t>
+          <t>What 1,000 successful people all said: "I was lucky."</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>그렇다면 나를 응원할 수밖에 (윈터 에디션)</t>
+          <t>럭키 LUCKY</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>김수민</t>
+          <t>김도윤</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
+          <t>2021-08-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>9791197037191</t>
+          <t>9791191891027</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -8414,22 +8451,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A Small Star, Still Shining (Midnight Edition)</t>
+          <t>Then I Have No Choice but to Cheer Myself On (Winter Edition)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A small, steady encouragement for everyone enduring the day.</t>
+          <t>Doing life my own way, and doing it right.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>작은 별이지만 빛나고 있어 (30만부 기념 미드나잇 에디션)</t>
+          <t>그렇다면 나를 응원할 수밖에 (윈터 에디션)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>소윤</t>
+          <t>김수민</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -8439,12 +8476,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>9791197037153</t>
+          <t>9791197037191</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -8456,22 +8493,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Let's Look at the Good Things Together</t>
+          <t>A Small Star, Still Shining (Midnight Edition)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The best things I've seen, offered to you.</t>
+          <t>A small, steady encouragement for everyone enduring the day.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>좋은 건 같이 봐요</t>
+          <t>작은 별이지만 빛나고 있어 (30만부 기념 미드나잇 에디션)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>엄지사진관</t>
+          <t>소윤</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -8481,12 +8518,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2021-01-27</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>9791197037146</t>
+          <t>9791197037153</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8498,22 +8535,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Hello, Precious One</t>
+          <t>Let's Look at the Good Things Together</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Everything about the preciousness you should hold on to.</t>
+          <t>The best things I've seen, offered to you.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>안녕, 소중한 사람</t>
+          <t>좋은 건 같이 봐요</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>정한경</t>
+          <t>엄지사진관</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -8523,12 +8560,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2021-01-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>9791197037122</t>
+          <t>9791197037146</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8540,40 +8577,82 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>Hello, Precious One</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Everything about the preciousness you should hold on to.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>안녕, 소중한 사람</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>정한경</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Essay</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>9791197037122</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>rights@thebookman.co.kr</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>I Love Myself</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>How to love others without losing yourself.</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>나는 나를 사랑한다</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>이숙명</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Essay</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>2020-06-24</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>9791197037108</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>rights@thebookman.co.kr</t>
         </is>

--- a/files/thebookman-booklist.xlsx
+++ b/files/thebookman-booklist.xlsx
@@ -5811,8 +5811,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Smart, Soulful, and Wholly Me</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>How to live fully as yourself in a world with no right answers.</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>나답게 똘똘하게</t>

--- a/files/thebookman-booklist.xlsx
+++ b/files/thebookman-booklist.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I122"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -535,63 +535,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다정한 안녕</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>달콤하고도 먹먹한 우리의 이별 준비</t>
-        </is>
-      </c>
+          <t>물각유주</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>마크 스티븐 포로 (지은이), 이유림 (옮긴이)</t>
+          <t>공백 (지은이)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9791124038932</t>
+          <t>9791124038871</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=403874634</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=405601995</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>품격 있는 대화를 위한 지식 브리핑 (10만 부 기념 특별 한정판)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>인생이 뜻대로 되지 않느냐고 철학자가 물었다</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>내 안의 행복을 찾아주는 에픽테토스의 철학 수업</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>김진 (지은이)</t>
+          <t>오기노 히로유키 (지은이), 가오리, 유카리 (그림), 황혜숙 (옮긴이)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -601,115 +601,119 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>25000</v>
+        <v>19000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9791124038413</t>
+          <t>9791124038925</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=404263026</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=405108521</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>여름</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>다정한 안녕</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>달콤하고도 먹먹한 우리의 이별 준비</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>이디스 워튼 (지은이), 민지현 (옮긴이)</t>
+          <t>마크 스티븐 포로 (지은이), 이유림 (옮긴이)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>머묾</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>19000</v>
+        <v>22000</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9791124038802</t>
+          <t>9791124038932</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401985055</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=403874634</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>위대한 개츠비</t>
+          <t>품격 있는 대화를 위한 지식 브리핑 (10만 부 기념 특별 한정판)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>프랜시스 스콧 피츠제럴드 (지은이), 이미정 (옮긴이)</t>
+          <t>김진 (지은이)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>머묾</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>19000</v>
+        <v>25000</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9791124038659</t>
+          <t>9791124038413</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401984756</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=404263026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>파리는 언제나 축제</t>
+          <t>여름</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>어니스트 헤밍웨이 (지은이), 권진아 (옮긴이)</t>
+          <t>이디스 워튼 (지은이), 민지현 (옮긴이)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -719,7 +723,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -732,39 +736,35 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9791124038666</t>
+          <t>9791124038802</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401985497</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401985055</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>단단히, 휩쓸리지 않고 살아간다는 것</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>흔들리는 시간을 지혜롭게 건너는 마음의 철학</t>
-        </is>
-      </c>
+          <t>위대한 개츠비</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>나디 미리안 (지은이), 김지유 (옮긴이)</t>
+          <t>프랜시스 스콧 피츠제럴드 (지은이), 이미정 (옮긴이)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>머묾</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -773,83 +773,79 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9791124038888</t>
+          <t>9791124038659</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=403488397</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401984756</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>머니 트렌드 2027</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>격변의 위기를 기회로 바꾸는 55가지 돈의 흐름</t>
-        </is>
-      </c>
+          <t>파리는 언제나 축제</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>정태익, 김도윤, 김광석, 김용섭, 김학렬, 박세익, 박정호, 이효석 (지은이)</t>
+          <t>어니스트 헤밍웨이 (지은이), 권진아 (옮긴이)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>머묾</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>27500</v>
+        <v>19000</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9791124038826</t>
+          <t>9791124038666</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401122536</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401985497</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>처음 만나는 철학의 세계</t>
+          <t>단단히, 휩쓸리지 않고 살아간다는 것</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>삶에 철학이 들어오는 순간</t>
+          <t>흔들리는 시간을 지혜롭게 건너는 마음의 철학</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>성창원 (지은이)</t>
+          <t>나디 미리안 (지은이), 김지유 (옮긴이)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -859,7 +855,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -867,115 +863,119 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9791124038833</t>
+          <t>9791124038888</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=402017704</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=403488397</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>똑똑한 사람은 어떻게 말하는가</t>
+          <t>머니 트렌드 2027</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>길게 말하지 않아도 신뢰받는 사람들의 말하기 전략</t>
+          <t>격변의 위기를 기회로 바꾸는 55가지 돈의 흐름</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>이시한 (지은이)</t>
+          <t>정태익, 김도윤, 김광석, 김용섭, 김학렬, 박세익, 박정호, 이효석 (지은이)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>22000</v>
+        <v>27500</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9791124038642</t>
+          <t>9791124038826</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=400007561</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=401122536</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>기억의 무늬</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>처음 만나는 철학의 세계</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>삶에 철학이 들어오는 순간</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>백희성 (지은이)</t>
+          <t>성창원 (지은이)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>19800</v>
+        <v>22000</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9791124038604</t>
+          <t>9791124038833</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=398993923</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=402017704</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>나는 도대체 왜 눈치를 볼까</t>
+          <t>똑똑한 사람은 어떻게 말하는가</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>타인의 기대에서 벗어나 원하는 삶을 사는 법</t>
+          <t>길게 말하지 않아도 신뢰받는 사람들의 말하기 전략</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>케리 올리치, 켈리 권터 (지은이), 김잔디 (옮긴이)</t>
+          <t>이시한 (지은이)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -990,52 +990,48 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9791124038536</t>
+          <t>9791124038642</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=397995935</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=400007561</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>만일 나에게 단 한 번의 아침이 남아 있다면 (굿모닝 에디션)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>오늘이 끝나기 전 반드시 깨달아야 할 것들</t>
-        </is>
-      </c>
+          <t>기억의 무늬</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>존 릴런드 (지은이), 최인하 (옮긴이)</t>
+          <t>백희성 (지은이)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1043,279 +1039,287 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9791193937112</t>
+          <t>9791124038604</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=398820063</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=398993923</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>너의 행복은 나의 기쁨이야</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>나는 도대체 왜 눈치를 볼까</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>타인의 기대에서 벗어나 원하는 삶을 사는 법</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>정한경 (지은이)</t>
+          <t>케리 올리치, 켈리 권터 (지은이), 김잔디 (옮긴이)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>19800</v>
+        <v>21000</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9791124038574</t>
+          <t>9791124038536</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396794390</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=397995935</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>여름 (썸머 에디션)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>만일 나에게 단 한 번의 아침이 남아 있다면 (굿모닝 에디션)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>오늘이 끝나기 전 반드시 깨달아야 할 것들</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>이디스 워튼 (지은이), 민지현 (옮긴이)</t>
+          <t>존 릴런드 (지은이), 최인하 (옮긴이)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>머묾</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>19000</v>
+        <v>19800</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9791124038581</t>
+          <t>9791193937112</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396568091</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=398820063</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>끌리는 사람의 비밀</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>마음을 움직이는 품위 있는 말과 태도</t>
-        </is>
-      </c>
+          <t>너의 행복은 나의 기쁨이야</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>조수빈 (지은이)</t>
+          <t>정한경 (지은이)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>22000</v>
+        <v>19800</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9791124038567</t>
+          <t>9791124038574</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396156367</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396794390</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>최소한의 습관</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>작은 시작으로 압도적 변화를 만드는 행동 공식</t>
-        </is>
-      </c>
+          <t>여름 (썸머 에디션)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>로버트 마우어 (지은이), 장원철 (옮긴이)</t>
+          <t>이디스 워튼 (지은이), 민지현 (옮긴이)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>머묾</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>19800</v>
+        <v>19000</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9791124038512</t>
+          <t>9791124038581</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=394919714</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396568091</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>이방인</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>끌리는 사람의 비밀</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>마음을 움직이는 품위 있는 말과 태도</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>알베르 카뮈 (지은이), 한수민 (옮긴이)</t>
+          <t>조수빈 (지은이)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>머묾</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>18000</v>
+        <v>22000</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9791124038390</t>
+          <t>9791124038567</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396164215</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396156367</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>프랑켄슈타인</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>최소한의 습관</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>작은 시작으로 압도적 변화를 만드는 행동 공식</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>메리 셸리 (지은이), 이미애 (옮긴이)</t>
+          <t>로버트 마우어 (지은이), 장원철 (옮긴이)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>머묾</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>21000</v>
+        <v>19800</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9791124038383</t>
+          <t>9791124038512</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396166191</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=394919714</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>올랜도</t>
+          <t>이방인</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>버지니아 울프 (지은이), 정해영 (옮긴이)</t>
+          <t>알베르 카뮈 (지은이), 한수민 (옮긴이)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1334,34 +1338,34 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>9791124038406</t>
+          <t>9791124038390</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396167382</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396164215</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>리치먼드힐의 이층 버스</t>
+          <t>프랑켄슈타인</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>이경진 (지은이)</t>
+          <t>메리 셸리 (지은이), 이미애 (옮긴이)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>머묾</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1375,79 +1379,75 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>19000</v>
+        <v>21000</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>9791124038499</t>
+          <t>9791124038383</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=394084608</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396166191</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>밤의 설계자</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>잠들기 전 15분, 미래를 바꾸는 밤 생각 습관</t>
-        </is>
-      </c>
+          <t>올랜도</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>폴커 부슈 (지은이), 이상희 (옮긴이)</t>
+          <t>버지니아 울프 (지은이), 정해영 (옮긴이)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>머묾</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>9791124038468</t>
+          <t>9791124038406</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=393318252</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=396167382</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>웨딩 피플</t>
+          <t>리치먼드힐의 이층 버스</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>앨리슨 에스파흐 (지은이), 김보람 (옮긴이)</t>
+          <t>이경진 (지은이)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1457,168 +1457,168 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>21000</v>
+        <v>19000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>9791124038437</t>
+          <t>9791124038499</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=392621945</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=394084608</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>아우슈비츠의 무용수</t>
+          <t>밤의 설계자</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>인생은 언제나 다시 선택할 수 있다</t>
+          <t>잠들기 전 15분, 미래를 바꾸는 밤 생각 습관</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>에디트 에바 에거 (지은이), 안진희 (옮긴이)</t>
+          <t>폴커 부슈 (지은이), 이상희 (옮긴이)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>24000</v>
+        <v>22000</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>9791124038352</t>
+          <t>9791124038468</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=391538652</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=393318252</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>오리지널 코드</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>상위 1%의 비밀, 나답게 일하고 나답게 성공하는 절대 공식</t>
-        </is>
-      </c>
+          <t>웨딩 피플</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>오은환 (지은이)</t>
+          <t>앨리슨 에스파흐 (지은이), 김보람 (옮긴이)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>9791124038369</t>
+          <t>9791124038437</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=390350168</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=392621945</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>미스터 나카모토</t>
+          <t>아우슈비츠의 무용수</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>비트코인의 창시자</t>
+          <t>인생은 언제나 다시 선택할 수 있다</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>벤저민 윌리스 (지은이), 이재득 (옮긴이)</t>
+          <t>에디트 에바 에거 (지은이), 안진희 (옮긴이)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>25000</v>
+        <v>24000</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>9791124038314</t>
+          <t>9791124038352</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=387309381</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=391538652</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>바다에서 온 소년</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>오리지널 코드</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>상위 1%의 비밀, 나답게 일하고 나답게 성공하는 절대 공식</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개럿 카 (지은이), 이은선 (옮긴이)</t>
+          <t>오은환 (지은이)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1628,38 +1628,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>19800</v>
+        <v>22000</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>9791124038338</t>
+          <t>9791124038369</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=388570776</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=390350168</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>사람을 얻는 힘 : 인간력</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>미스터 나카모토</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>비트코인의 창시자</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>다사카 히로시 (지은이), 장은주 (옮긴이)</t>
+          <t>벤저민 윌리스 (지은이), 이재득 (옮긴이)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1669,42 +1673,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9791124038253</t>
+          <t>9791124038314</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=387645690</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=387309381</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>당신은 가치 있다</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>마음을 회복하는 자기 돌봄의 심리학</t>
-        </is>
-      </c>
+          <t>바다에서 온 소년</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>안드레아스 크누프 (지은이), 박병화 (옮긴이)</t>
+          <t>개럿 카 (지은이), 이은선 (옮긴이)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1727,79 +1727,75 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9791124038291</t>
+          <t>9791124038338</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=386487867</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=388570776</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>삶의 끝에서 만난 수업</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>죽음이 가르쳐준 후회 없는 삶</t>
-        </is>
-      </c>
+          <t>사람을 얻는 힘 : 인간력</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>에리카 하야사키 (지은이), 이은주 (옮긴이)</t>
+          <t>다사카 히로시 (지은이), 장은주 (옮긴이)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9791124038284</t>
+          <t>9791124038253</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=385616736</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=387645690</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>모든 것은 별에서 시작되었다</t>
+          <t>당신은 가치 있다</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>천문학자가 바라본 우주와 인류의 발자취</t>
+          <t>마음을 회복하는 자기 돌봄의 심리학</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>조앤 베이커 (지은이), 고유경 (옮긴이)</t>
+          <t>안드레아스 크누프 (지은이), 박병화 (옮긴이)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1809,37 +1805,37 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>22000</v>
+        <v>19800</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>9791124038277</t>
+          <t>9791124038291</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=385203905</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=386487867</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>모두에게 사랑받을 필요는 없다</t>
+          <t>삶의 끝에서 만난 수업</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>비교와 눈치에서 해방되는 삶의 기술</t>
+          <t>죽음이 가르쳐준 후회 없는 삶</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>웨인 다이어 (지은이), 장원철 (옮긴이)</t>
+          <t>에리카 하야사키 (지은이), 이은주 (옮긴이)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1849,12 +1845,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1862,112 +1858,120 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>9791124038185</t>
+          <t>9791124038284</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384701650</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=385616736</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>나의 완벽한 장례식</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>모든 것은 별에서 시작되었다</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>천문학자가 바라본 우주와 인류의 발자취</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>조현선 (지은이)</t>
+          <t>조앤 베이커 (지은이), 고유경 (옮긴이)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>19000</v>
+        <v>22000</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>9791124038192</t>
+          <t>9791124038277</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=383575374</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=385203905</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>첫눈, 고백</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>모두에게 사랑받을 필요는 없다</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>비교와 눈치에서 해방되는 삶의 기술</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>기 드 모파상 (지은이), 구영옥 (옮긴이)</t>
+          <t>웨인 다이어 (지은이), 장원철 (옮긴이)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>머묾</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>19000</v>
+        <v>22000</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>9791124038154</t>
+          <t>9791124038185</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=381528041</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384701650</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>사랑에 관한 짧은 이야기</t>
+          <t>나의 완벽한 장례식</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>프랜시스 스콧 피츠제럴드 (지은이), 정지현 (옮긴이)</t>
+          <t>조현선 (지은이)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>머묾</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1977,7 +1981,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1985,25 +1989,25 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>9791124038161</t>
+          <t>9791124038192</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=381620936</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=383575374</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>첫사랑</t>
+          <t>첫눈, 고백</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>이반 세르게예비치 투르게네프 (지은이), 승주연 (옮긴이)</t>
+          <t>기 드 모파상 (지은이), 구영옥 (옮긴이)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2022,240 +2026,240 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>18000</v>
+        <v>19000</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9791124038147</t>
+          <t>9791124038154</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=381528407</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=381528041</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>캘리쌤의 루틴 잉글리시</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>하루 10분, 90일 영어 습관 프로젝트</t>
-        </is>
-      </c>
+          <t>사랑에 관한 짧은 이야기</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>캘리쌤 (지은이)</t>
+          <t>프랜시스 스콧 피츠제럴드 (지은이), 정지현 (옮긴이)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>머묾</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>그 밖의 책</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>9791124038123</t>
+          <t>9791124038161</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=379524547</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=381620936</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>마일리지 아워</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>삶의 격을 높이는 인생 설계의 기술</t>
-        </is>
-      </c>
+          <t>첫사랑</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>최유나 (지은이)</t>
+          <t>이반 세르게예비치 투르게네프 (지은이), 승주연 (옮긴이)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>머묾</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>9791124038093</t>
+          <t>9791124038147</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=377166373</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=381528407</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>석세스</t>
+          <t>캘리쌤의 루틴 잉글리시</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>지금 시작하는 목표 설계의 비밀</t>
+          <t>하루 10분, 90일 영어 습관 프로젝트</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>하이디 그랜트 할버슨 (지은이), 장원철 (옮긴이)</t>
+          <t>캘리쌤 (지은이)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>그 밖의 책</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>9791124038086</t>
+          <t>9791124038123</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=374615177</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=379524547</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 10</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>마일리지 아워</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>삶의 격을 높이는 인생 설계의 기술</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>나관중 (지은이), 백남원 (그림), 박상률 (옮긴이)</t>
+          <t>최유나 (지은이)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>18800</v>
+        <v>22000</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>9791193937969</t>
+          <t>9791124038093</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384185742</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=377166373</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 9</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>석세스</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>지금 시작하는 목표 설계의 비밀</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>나관중 (지은이), 백남원 (그림), 박상률 (옮긴이)</t>
+          <t>하이디 그랜트 할버슨 (지은이), 장원철 (옮긴이)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>18800</v>
+        <v>21000</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>9791193937952</t>
+          <t>9791124038086</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384185675</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=374615177</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 8</t>
+          <t>박상률 완역 삼국지 10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2284,19 +2288,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>9791193937945</t>
+          <t>9791193937969</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184694</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384185742</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 7</t>
+          <t>박상률 완역 삼국지 9</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2325,19 +2329,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>9791193937938</t>
+          <t>9791193937952</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184639</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384185675</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 6</t>
+          <t>박상률 완역 삼국지 8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2366,19 +2370,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>9791193937921</t>
+          <t>9791193937945</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184552</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184694</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 5</t>
+          <t>박상률 완역 삼국지 7</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2407,19 +2411,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>9791193937914</t>
+          <t>9791193937938</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184384</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184639</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 4</t>
+          <t>박상률 완역 삼국지 6</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2448,19 +2452,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>9791193937907</t>
+          <t>9791193937921</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184368</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184552</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 3</t>
+          <t>박상률 완역 삼국지 5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2489,19 +2493,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>9791193937891</t>
+          <t>9791193937914</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184313</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184384</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 2</t>
+          <t>박상률 완역 삼국지 4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2530,19 +2534,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>9791193937884</t>
+          <t>9791193937907</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184247</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184368</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 1</t>
+          <t>박상률 완역 삼국지 3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2571,26 +2575,22 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>9791193937877</t>
+          <t>9791193937891</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384183907</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184313</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>박상률 완역 삼국지 세트</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>전10권</t>
-        </is>
-      </c>
+          <t>박상률 완역 삼국지 2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>나관중 (지은이), 백남원 (그림), 박상률 (옮긴이)</t>
@@ -2612,33 +2612,29 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>188000</v>
+        <v>18800</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>9791193937860</t>
+          <t>9791193937884</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384182721</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384184247</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>때로 외로움은 삶의 방패가 된다</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>타인에게 상처받지 않고 나를 지키는 고독의 힘</t>
-        </is>
-      </c>
+          <t>박상률 완역 삼국지 1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>에노모토 히로아키 (지은이), 장은주 (옮긴이)</t>
+          <t>나관중 (지은이), 백남원 (그림), 박상률 (옮긴이)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2648,7 +2644,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2657,34 +2653,38 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>19000</v>
+        <v>18800</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>9791124038024</t>
+          <t>9791193937877</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=374895246</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384183907</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>브로큰 컨트리</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>박상률 완역 삼국지 세트</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>전10권</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>클레어 레슬리 홀 (지은이), 박지선 (옮긴이)</t>
+          <t>나관중 (지은이), 백남원 (그림), 박상률 (옮긴이)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2694,258 +2694,258 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>19500</v>
+        <v>188000</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>9791193937853</t>
+          <t>9791193937860</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=373453855</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=384182721</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>어른의 품위</t>
+          <t>때로 외로움은 삶의 방패가 된다</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>진짜 어른이 되기 위해 지켜야 할 삶의 태도</t>
+          <t>타인에게 상처받지 않고 나를 지키는 고독의 힘</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>최서영 (지은이)</t>
+          <t>에노모토 히로아키 (지은이), 장은주 (옮긴이)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>19500</v>
+        <v>19000</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>9791193937693</t>
+          <t>9791124038024</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=372567841</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=374895246</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>머니 트렌드 2026</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>위기 속 돈의 흐름을 지배하는 50가지 생존 공식</t>
-        </is>
-      </c>
+          <t>브로큰 컨트리</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>김도윤, 정태익, 김광석, 김승주, 김용섭, 김학렬(빠숑), 김현준, 최재붕 (지은이)</t>
+          <t>클레어 레슬리 홀 (지은이), 박지선 (옮긴이)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>9791193937686</t>
+          <t>9791193937853</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=370922288</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=373453855</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>처음 만나는 양자의 세계</t>
+          <t>어른의 품위</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>양자 역학부터 양자 컴퓨터 까지</t>
+          <t>진짜 어른이 되기 위해 지켜야 할 삶의 태도</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>채은미 (지은이)</t>
+          <t>최서영 (지은이)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>19000</v>
+        <v>19500</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>9791193937990</t>
+          <t>9791193937693</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=372088796</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=372567841</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>파이브 센스</t>
+          <t>머니 트렌드 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>소진된 일상에서 행복을 되찾는 마음 회복법</t>
+          <t>위기 속 돈의 흐름을 지배하는 50가지 생존 공식</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>그레첸 루빈 (지은이), 김잔디 (옮긴이)</t>
+          <t>김도윤, 정태익, 김광석, 김승주, 김용섭, 김학렬(빠숑), 김현준, 최재붕 (지은이)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>22000</v>
+        <v>26000</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>9791193937846</t>
+          <t>9791193937686</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=369930840</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=370922288</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>월요일 수요일 토요일</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>처음 만나는 양자의 세계</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>양자 역학부터 양자 컴퓨터 까지</t>
+        </is>
+      </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>페트라 펠리니 (지은이), 전은경 (옮긴이)</t>
+          <t>채은미 (지은이)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>19500</v>
+        <v>19000</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>9791193937822</t>
+          <t>9791193937990</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=369095688</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=372088796</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>시선 너머의 지식</t>
+          <t>파이브 센스</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>9가지 질문으로 읽는 숨겨진 세계</t>
+          <t>소진된 일상에서 행복을 되찾는 마음 회복법</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>윤수용 (지은이)</t>
+          <t>그레첸 루빈 (지은이), 김잔디 (옮긴이)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2968,153 +2968,157 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>9791193937785</t>
+          <t>9791193937846</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=368128493</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=369930840</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>행복 강박</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>행복 과잉 시대에서 잃어버린 진짜 삶을 찾는 법</t>
-        </is>
-      </c>
+          <t>월요일 수요일 토요일</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>올리버 버크먼 (지은이), 정지인 (옮긴이)</t>
+          <t>페트라 펠리니 (지은이), 전은경 (옮긴이)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>22000</v>
+        <v>19500</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>9791193937778</t>
+          <t>9791193937822</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=366392151</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=369095688</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>메리골드 아틀리에 컬렉션 특별 한정판 세트</t>
+          <t>시선 너머의 지식</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>전3권</t>
+          <t>9가지 질문으로 읽는 숨겨진 세계</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>윤정은 (지은이)</t>
+          <t>윤수용 (지은이)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>54000</v>
+        <v>22000</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>9791193937754</t>
+          <t>9791193937785</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365445143</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=368128493</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>메리골드 마음 식물원 (아틀리에 컬렉션)</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>행복 강박</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>행복 과잉 시대에서 잃어버린 진짜 삶을 찾는 법</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>윤정은 (지은이)</t>
+          <t>올리버 버크먼 (지은이), 정지인 (옮긴이)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>18000</v>
+        <v>22000</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>9791193937723</t>
+          <t>9791193937778</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365443154</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=366392151</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>메리골드 마음 사진관 (아틀리에 컬렉션)</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>메리골드 아틀리에 컬렉션 특별 한정판 세트</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>전3권</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr">
         <is>
           <t>윤정은 (지은이)</t>
@@ -3136,23 +3140,23 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>18000</v>
+        <v>54000</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>9791193937730</t>
+          <t>9791193937754</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365443349</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365445143</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>메리골드 마음 세탁소 (아틀리에 컬렉션)</t>
+          <t>메리골드 마음 식물원 (아틀리에 컬렉션)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3181,74 +3185,66 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>9791193937310</t>
+          <t>9791193937723</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365443113</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365443154</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>왓츠 유어 드림</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>인생을 뒤바꾸는 단 하나의 질문</t>
-        </is>
-      </c>
+          <t>메리골드 마음 사진관 (아틀리에 컬렉션)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>사이먼 스큅 (지은이), 최인하 (옮긴이)</t>
+          <t>윤정은 (지은이)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>9791193937709</t>
+          <t>9791193937730</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=364723142</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365443349</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>우리의 낙원에서 만나자</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>이 계절을 함께 건너는 당신에게</t>
-        </is>
-      </c>
+          <t>메리골드 마음 세탁소 (아틀리에 컬렉션)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>하태완 (지은이)</t>
+          <t>윤정은 (지은이)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3258,47 +3254,47 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>19500</v>
+        <v>18000</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>9791193937655</t>
+          <t>9791193937310</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363874338</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=365443113</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>코어 씽킹 Core Thinking</t>
+          <t>왓츠 유어 드림</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>일의 본질을 꿰뚫는 생각의 기술</t>
+          <t>인생을 뒤바꾸는 단 하나의 질문</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>김범섭 (지은이)</t>
+          <t>사이먼 스큅 (지은이), 최인하 (옮긴이)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3308,7 +3304,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -3316,120 +3312,124 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>9791193937624</t>
+          <t>9791193937709</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363358764</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=364723142</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>당신은 언제나 괜찮다</t>
+          <t>우리의 낙원에서 만나자</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>흔들리는 시간을 넘어 단단히 나를 세우는 법</t>
+          <t>이 계절을 함께 건너는 당신에게</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>이현수 (지은이)</t>
+          <t>하태완 (지은이)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>19800</v>
+        <v>19500</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>9791193937617</t>
+          <t>9791193937655</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363057823</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363874338</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>다 좋아질 거야, 행복이 쏟아질 만큼</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
+          <t>코어 씽킹 Core Thinking</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>일의 본질을 꿰뚫는 생각의 기술</t>
+        </is>
+      </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>길연우 (지은이)</t>
+          <t>김범섭 (지은이)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>19800</v>
+        <v>22000</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>9791193937594</t>
+          <t>9791193937624</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=362220234</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363358764</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>무엇을 사랑하고 어떻게 행복할 것인가</t>
+          <t>당신은 언제나 괜찮다</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>행복을 습관으로 만드는 하버드 명강의</t>
+          <t>흔들리는 시간을 넘어 단단히 나를 세우는 법</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>유키 소노마 (지은이), 정은희 (옮긴이)</t>
+          <t>이현수 (지은이)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3439,37 +3439,33 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>22000</v>
+        <v>19800</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>9791193937587</t>
+          <t>9791193937617</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=361430765</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363057823</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>나를 쓰는 시간</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>한 줄의 기록이 삶을 바꾼다</t>
-        </is>
-      </c>
+          <t>다 좋아질 거야, 행복이 쏟아질 만큼</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>장예원 (지은이)</t>
+          <t>길연우 (지은이)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3479,38 +3475,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>22000</v>
+        <v>19800</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>9791193937365</t>
+          <t>9791193937594</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=361643111</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=362220234</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>모든 걸음에는 이유가 있다</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
+          <t>무엇을 사랑하고 어떻게 행복할 것인가</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>행복을 습관으로 만드는 하버드 명강의</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>김아영 (지은이)</t>
+          <t>유키 소노마 (지은이), 정은희 (옮긴이)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3520,57 +3520,57 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>19800</v>
+        <v>22000</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>9791193937563</t>
+          <t>9791193937587</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=361151650</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=361430765</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI 패권 전쟁</t>
+          <t>나를 쓰는 시간</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>챗GPT 딥시크의 미래와 AI 그 이후</t>
+          <t>한 줄의 기록이 삶을 바꾼다</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>이시한 (지은이)</t>
+          <t>장예원 (지은이)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -3578,29 +3578,25 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>9791193937549</t>
+          <t>9791193937365</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=357398970</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=361643111</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>스위트 스팟</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>인생의 숨은 기회를 찾는 9가지 통찰</t>
-        </is>
-      </c>
+          <t>모든 걸음에는 이유가 있다</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>샘 리처드 (지은이), 김수민 (옮긴이)</t>
+          <t>김아영 (지은이)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3610,12 +3606,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -3623,29 +3619,29 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>9791193937532</t>
+          <t>9791193937563</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=358119007</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=361151650</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>성난 파도 다스리기</t>
+          <t>AI 패권 전쟁</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>소란한 마음을 고요하게 하는 365가지 삶의 지혜</t>
+          <t>챗GPT 딥시크의 미래와 AI 그 이후</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>덩 밍다오 (지은이), 김희균 (옮긴이)</t>
+          <t>이시한 (지은이)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3655,12 +3651,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -3668,85 +3664,89 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>9791193937433</t>
+          <t>9791193937549</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=355338819</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=357398970</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>내가 원하는 것을 나도 모를 때</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>스위트 스팟</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>인생의 숨은 기회를 찾는 9가지 통찰</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>전승환 (지은이)</t>
+          <t>샘 리처드 (지은이), 김수민 (옮긴이)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>22000</v>
+        <v>19800</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>9791193937150</t>
+          <t>9791193937532</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=354981569</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=358119007</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>왜 그들만 부자가 되는가</t>
+          <t>성난 파도 다스리기</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>부의 격차를 좁히는 진짜 돈의 모습</t>
+          <t>소란한 마음을 고요하게 하는 365가지 삶의 지혜</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>필립 바구스, 안드레아스 마르크바르트 (지은이), 배진아 (옮긴이)</t>
+          <t>덩 밍다오 (지은이), 김희균 (옮긴이)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -3754,29 +3754,25 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>9791193937396</t>
+          <t>9791193937433</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=354574933</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=355338819</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>새들이 남쪽으로 가는 날</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2024 스웨덴 올해의 도서상 수상작</t>
-        </is>
-      </c>
+          <t>내가 원하는 것을 나도 모를 때</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>리사 리드센 (지은이), 손화수 (옮긴이)</t>
+          <t>전승환 (지은이)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3786,57 +3782,57 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>19500</v>
+        <v>22000</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>9791193937372</t>
+          <t>9791193937150</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=352764746</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=354981569</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>삶의 태도</t>
+          <t>왜 그들만 부자가 되는가</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>흔들림 없이 나아가는</t>
+          <t>부의 격차를 좁히는 진짜 돈의 모습</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>반건호 (지은이)</t>
+          <t>필립 바구스, 안드레아스 마르크바르트 (지은이), 배진아 (옮긴이)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -3844,74 +3840,74 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>9791193937402</t>
+          <t>9791193937396</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=353472576</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=354574933</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>인생을 자유롭게 하는 것들</t>
+          <t>새들이 남쪽으로 가는 날</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>가슴 뛰는 삶을 향해 가는 최우선의 행복</t>
+          <t>2024 스웨덴 올해의 도서상 수상작</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>나용민, 유숙현 (지은이)</t>
+          <t>리사 리드센 (지은이), 손화수 (옮긴이)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>18000</v>
+        <v>19500</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>9791193937389</t>
+          <t>9791193937372</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=353117247</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=352764746</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>쉼과 나아감에 대하여</t>
+          <t>삶의 태도</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>인생의 오아시스를 만나는 예일대 명강의</t>
+          <t>흔들림 없이 나아가는</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>마릴린 폴 (지은이), 김태훈 (옮긴이)</t>
+          <t>반건호 (지은이)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3921,102 +3917,102 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>19800</v>
+        <v>22000</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>9791193937341</t>
+          <t>9791193937402</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=351959853</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=353472576</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>영국 아빠 피터의 하루 3분 영어 대화 (스프링)</t>
+          <t>인생을 자유롭게 하는 것들</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>스스로 말하고 표현하는 영어 회화 일력</t>
+          <t>가슴 뛰는 삶을 향해 가는 최우선의 행복</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>피터 빈트 (지은이)</t>
+          <t>나용민, 유숙현 (지은이)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>북크레용</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>자녀교육</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>25000</v>
+        <v>18000</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>9791193937280</t>
+          <t>9791193937389</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=350405920</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=353117247</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>질투라는 감옥</t>
+          <t>쉼과 나아감에 대하여</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>우리는 왜 타인에게 휘둘리는가</t>
+          <t>인생의 오아시스를 만나는 예일대 명강의</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>야마모토 케이 (지은이), 최주연 (옮긴이)</t>
+          <t>마릴린 폴 (지은이), 김태훈 (옮긴이)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -4024,44 +4020,44 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>9791193937259</t>
+          <t>9791193937341</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=348985847</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=351959853</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>머니 트렌드 2025</t>
+          <t>영국 아빠 피터의 하루 3분 영어 대화 (스프링)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>새로운 부의 기회를 선점할 55가지 성공 시나리오</t>
+          <t>스스로 말하고 표현하는 영어 회화 일력</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>정태익, 김도윤, 김광석, 김용섭, 김현준, 정수종, 채상욱, 최재붕 (지은이)</t>
+          <t>피터 빈트 (지은이)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북크레용</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>자녀교육</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -4069,44 +4065,44 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>9791193937211</t>
+          <t>9791193937280</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=345965820</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=350405920</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>마음이 부자인 아이는 어떻게 성장하는가</t>
+          <t>질투라는 감옥</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>행복할 줄 아는 아이로 키우는 정서 육아법</t>
+          <t>우리는 왜 타인에게 휘둘리는가</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>박소영 (지은이)</t>
+          <t>야마모토 케이 (지은이), 최주연 (옮긴이)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>북크레용</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>자녀교육</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -4114,261 +4110,265 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>9791193937228</t>
+          <t>9791193937259</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=346892914</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=348985847</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>엄마에게 안부를 묻는 밤</t>
+          <t>머니 트렌드 2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>언제나 내 편인 이 세상 단 한 사람</t>
+          <t>새로운 부의 기회를 선점할 55가지 성공 시나리오</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>박애희 (지은이)</t>
+          <t>정태익, 김도윤, 김광석, 김용섭, 김현준, 정수종, 채상욱, 최재붕 (지은이)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>북파머스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>18800</v>
+        <v>25000</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>9791193937242</t>
+          <t>9791193937211</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=346467345</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=345965820</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>빛이 이끄는 곳으로</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>마음이 부자인 아이는 어떻게 성장하는가</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>행복할 줄 아는 아이로 키우는 정서 육아법</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>백희성 (지은이)</t>
+          <t>박소영 (지은이)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북크레용</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>소설</t>
+          <t>자녀교육</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>18800</v>
+        <v>19800</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>9791193937198</t>
+          <t>9791193937228</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=344497704</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=346892914</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>호감의 시작 (트윙클 에디션)</t>
+          <t>엄마에게 안부를 묻는 밤</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>관계, 일, 인생이 풀리는 매력의 법칙</t>
+          <t>언제나 내 편인 이 세상 단 한 사람</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>희렌최 (지은이)</t>
+          <t>박애희 (지은이)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북파머스</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>18500</v>
+        <v>18800</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>9791193937143</t>
+          <t>9791193937242</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=342932323</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=346467345</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>나는 도대체 왜 피곤할까</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>이 죽일 놈의 피로와 결별하는 법</t>
-        </is>
-      </c>
+          <t>빛이 이끄는 곳으로</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>에이미 샤 (지은이), 김잔디 (옮긴이)</t>
+          <t>백희성 (지은이)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>소설</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>19800</v>
+        <v>18800</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>9791193937136</t>
+          <t>9791193937198</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=342083093</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=344497704</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>그럼에도 불구하고 나는 내가 좋았어</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>호감의 시작 (트윙클 에디션)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>관계, 일, 인생이 풀리는 매력의 법칙</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>박채린 (지은이)</t>
+          <t>희렌최 (지은이)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>18000</v>
+        <v>18500</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>9791193937105</t>
+          <t>9791193937143</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=340511549</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=342932323</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>부자의 마지막 가르침 (30만 부 리커버)</t>
+          <t>나는 도대체 왜 피곤할까</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>삶의 자유를 위한 부의 알고리즘</t>
+          <t>이 죽일 놈의 피로와 결별하는 법</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>다우치 마나부 (지은이), 김슬기 (옮긴이)</t>
+          <t>에이미 샤 (지은이), 김잔디 (옮긴이)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -4376,299 +4376,295 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>9791193937068</t>
+          <t>9791193937136</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363272157</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=342083093</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>똑똑한 아이는 어떻게 생각하고 질문하는가</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>사고력 실종의 시대, 주도적인 아이들의 생존 전략</t>
-        </is>
-      </c>
+          <t>그럼에도 불구하고 나는 내가 좋았어</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>이시한 (지은이)</t>
+          <t>박채린 (지은이)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>북크레용</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>자녀교육</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>19800</v>
+        <v>18000</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>9791193937037</t>
+          <t>9791193937105</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=337128010</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=340511549</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>사랑받는 이기주의자</t>
+          <t>부자의 마지막 가르침 (30만 부 리커버)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>나를 지키며 사랑받는 관계의 기술</t>
+          <t>삶의 자유를 위한 부의 알고리즘</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>박코 (지은이)</t>
+          <t>다우치 마나부 (지은이), 김슬기 (옮긴이)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>18000</v>
+        <v>19800</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>9791193937051</t>
+          <t>9791193937068</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=338458067</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=363272157</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>내가 천 개의 인생에서 배운 것들</t>
+          <t>똑똑한 아이는 어떻게 생각하고 질문하는가</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>돈, 명예, 시간 그 무엇보다 소중한 것에 관하여</t>
+          <t>사고력 실종의 시대, 주도적인 아이들의 생존 전략</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>김도윤 (지은이)</t>
+          <t>이시한 (지은이)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북크레용</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자녀교육</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>18000</v>
+        <v>19800</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>9791198530394</t>
+          <t>9791193937037</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=337269711</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=337128010</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>양수인간</t>
+          <t>사랑받는 이기주의자</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>삶의 격을 높이는 내면 변화 심리학</t>
+          <t>나를 지키며 사랑받는 관계의 기술</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>최설민 (지은이)</t>
+          <t>박코 (지은이)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>19800</v>
+        <v>18000</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>9791193937006</t>
+          <t>9791193937051</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=336173615</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=338458067</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>무엇이 나를 행복하게 만드는가</t>
+          <t>내가 천 개의 인생에서 배운 것들</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>인생의 절반쯤 왔을 때 깨닫게 되는 것들</t>
+          <t>돈, 명예, 시간 그 무엇보다 소중한 것에 관하여</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>리처드 J. 라이더, 데이비드 A. 샤피로 (지은이), 김정홍 (옮긴이)</t>
+          <t>김도윤 (지은이)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>19800</v>
+        <v>18000</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>9791198530356</t>
+          <t>9791198530394</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=334885758</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=337269711</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>노인의 꿈 : 첫 번째 이야기</t>
+          <t>양수인간</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>황혼을 향해 걷는 우리 모두의 이야기</t>
+          <t>삶의 격을 높이는 내면 변화 심리학</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>백원달 (지은이)</t>
+          <t>최설민 (지은이)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>북플레저</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>그 밖의 책</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>23000</v>
+        <v>19800</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>9791191891478</t>
+          <t>9791193937006</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=335184922</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=336173615</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>노인의 꿈 : 두 번째 이야기</t>
+          <t>무엇이 나를 행복하게 만드는가</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>황혼을 향해 걷는 우리 모두의 이야기</t>
+          <t>인생의 절반쯤 왔을 때 깨닫게 되는 것들</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>백원달 (지은이)</t>
+          <t>리처드 J. 라이더, 데이비드 A. 샤피로 (지은이), 김정홍 (옮긴이)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4678,42 +4674,42 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>그 밖의 책</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>23000</v>
+        <v>19800</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>9791191891485</t>
+          <t>9791198530356</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=335185323</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=334885758</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>똑똑한 사람은 어떻게 생각하고 질문하는가</t>
+          <t>노인의 꿈 : 첫 번째 이야기</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>사고력 실종의 시대, 앞서가는 사람들의 생존 전략</t>
+          <t>황혼을 향해 걷는 우리 모두의 이야기</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>이시한 (지은이)</t>
+          <t>백원달 (지은이)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4723,42 +4719,42 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>그 밖의 책</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>19800</v>
+        <v>23000</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>9791191891492</t>
+          <t>9791191891478</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=332269449</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=335184922</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>산책하듯 가볍게 (풀빛 에디션)</t>
+          <t>노인의 꿈 : 두 번째 이야기</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>인생에서 여유를 찾는 당신에게 건네는 말</t>
+          <t>황혼을 향해 걷는 우리 모두의 이야기</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>정우성 (지은이)</t>
+          <t>백원달 (지은이)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4768,132 +4764,132 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>그 밖의 책</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>17500</v>
+        <v>23000</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>9791191891447</t>
+          <t>9791191891485</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=388109982</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=335185323</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>하는 일마다 잘되리라</t>
+          <t>똑똑한 사람은 어떻게 생각하고 질문하는가</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>당신이 어디에 있든 무엇을 하든</t>
+          <t>사고력 실종의 시대, 앞서가는 사람들의 생존 전략</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>전승환 (지은이)</t>
+          <t>이시한 (지은이)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>18000</v>
+        <v>19800</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>9791198530301</t>
+          <t>9791191891492</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=328632910</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=332269449</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>머니 트렌드 2024</t>
+          <t>산책하듯 가볍게 (풀빛 에디션)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>57가지 키워드로 전망하는 대한민국 돈의 흐름</t>
+          <t>인생에서 여유를 찾는 당신에게 건네는 말</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>김도윤, 정태익, 김용섭, 김현준, 전영수, 채상욱, 최재붕, 홍춘욱 (지은이)</t>
+          <t>정우성 (지은이)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북플레저</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>25000</v>
+        <v>17500</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>9791191891416</t>
+          <t>9791191891447</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=324498127</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=388109982</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>꽃은 누구에게나 핀다</t>
+          <t>하는 일마다 잘되리라</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>오늘부터 내 삶을 바꾸는 자기 확신 에세이, 매일 더 설레는 날을 살게 될 당신에</t>
+          <t>당신이 어디에 있든 무엇을 하든</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>오은환 (지은이)</t>
+          <t>전승환 (지은이)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4908,82 +4904,82 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>17500</v>
+        <v>18000</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>9791191891409</t>
+          <t>9791198530301</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=324723810</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=328632910</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>나는 너랑 노는 게 제일 좋아</t>
+          <t>머니 트렌드 2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>아끼고 고맙고 사랑하는 당신에게</t>
+          <t>57가지 키워드로 전망하는 대한민국 돈의 흐름</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>하태완 (지은이)</t>
+          <t>김도윤, 정태익, 김용섭, 김현준, 전영수, 채상욱, 최재붕, 홍춘욱 (지은이)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>17500</v>
+        <v>25000</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>9791191891362</t>
+          <t>9791191891416</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=320503944</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=324498127</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>마음의 자유</t>
+          <t>꽃은 누구에게나 핀다</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>행복이란 마음이 어디에도 얽매이지 않는 것</t>
+          <t>오늘부터 내 삶을 바꾸는 자기 확신 에세이, 매일 더 설레는 날을 살게 될 당신에</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>정윤 (지은이)</t>
+          <t>오은환 (지은이)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4998,37 +4994,37 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>17000</v>
+        <v>17500</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>9791191891355</t>
+          <t>9791191891409</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=318438169</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=324723810</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>찌그러져도 괜찮아</t>
+          <t>나는 너랑 노는 게 제일 좋아</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>이미 찌그러진 오리가</t>
+          <t>아끼고 고맙고 사랑하는 당신에게</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>찌오(임임) (지은이)</t>
+          <t>하태완 (지은이)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5043,74 +5039,82 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>17000</v>
+        <v>17500</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>9791191891324</t>
+          <t>9791191891362</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=315987317</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=320503944</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>인생에서 가장 후회되는 게 뭐냐고 묻는다면</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>마음의 자유</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>행복이란 마음이 어디에도 얽매이지 않는 것</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>노우티 (지은이)</t>
+          <t>정윤 (지은이)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>인문·교양</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>17500</v>
+        <v>17000</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>9791191891331</t>
+          <t>9791191891355</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=315418702</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=318438169</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>당신과 아침에 싸우면 밤에는 입맞출 겁니다</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
+          <t>찌그러져도 괜찮아</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>이미 찌그러진 오리가</t>
+        </is>
+      </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>유래혁 (지은이)</t>
+          <t>찌오(임임) (지은이)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5125,7 +5129,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -5133,25 +5137,25 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>9791191891263</t>
+          <t>9791191891324</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=313695065</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=315987317</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GPT 제너레이션 : 챗GPT가 바꿀 우리 인류의 미래</t>
+          <t>인생에서 가장 후회되는 게 뭐냐고 묻는다면</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>이시한 (지은이)</t>
+          <t>노우티 (지은이)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5161,42 +5165,38 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>인문·교양</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>19000</v>
+        <v>17500</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>9791191891270</t>
+          <t>9791191891331</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=310813322</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=315418702</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>오둥이입니다만!</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>나는 세상에서 가장 행복한 오리</t>
-        </is>
-      </c>
+          <t>당신과 아침에 싸우면 밤에는 입맞출 겁니다</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>송 스튜디오 (지은이)</t>
+          <t>유래혁 (지은이)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -5219,70 +5219,70 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>9791191891256</t>
+          <t>9791191891263</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=310407734</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=313695065</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>행복을 담아줄게</t>
+          <t>GPT 제너레이션 : 챗GPT가 바꿀 우리 인류의 미래</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>나란 (지은이)</t>
+          <t>이시한 (지은이)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>9791191891249</t>
+          <t>9791191891270</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=309568882</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=310813322</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>나는 오늘의 내가 좋아</t>
+          <t>오둥이입니다만!</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>긍정토끼 몰랑이의 몰랑몰랑 마음 일기</t>
+          <t>나는 세상에서 가장 행복한 오리</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>윤혜지(하얀오리) (지은이)</t>
+          <t>송 스튜디오 (지은이)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5297,78 +5297,78 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>16000</v>
+        <v>17000</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>9791191891126</t>
+          <t>9791191891256</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=306216745</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=310407734</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>머니 트렌드 2023</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>45가지 키워드로 전망하는 대한민국 돈의 흐름</t>
-        </is>
-      </c>
+          <t>행복을 담아줄게</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>부동산읽어주는남자(정태익), 김도윤, 김경민, 김상균, 전영수, 최준철, 홍춘욱 (지은이)</t>
+          <t>나란 (지은이)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>북모먼트</t>
+          <t>북로망스</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>경제·경영</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2023-01-30</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>19000</v>
+        <v>16000</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>9791191891232</t>
+          <t>9791191891249</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=304588805</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=309568882</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>잘될 수밖에 없는 너에게</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
+          <t>나는 오늘의 내가 좋아</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>긍정토끼 몰랑이의 몰랑몰랑 마음 일기</t>
+        </is>
+      </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>최서영 (지은이)</t>
+          <t>윤혜지(하얀오리) (지은이)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5383,78 +5383,78 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>19500</v>
+        <v>16000</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>9791191891201</t>
+          <t>9791191891126</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=299808248</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=306216745</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>나로서 충분히 괜찮은 사람</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>머니 트렌드 2023</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>45가지 키워드로 전망하는 대한민국 돈의 흐름</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>김재식 (지은이)</t>
+          <t>부동산읽어주는남자(정태익), 김도윤, 김경민, 김상균, 전영수, 최준철, 홍춘욱 (지은이)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>북로망스</t>
+          <t>북모먼트</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>경제·경영</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>9791191891096</t>
+          <t>9791191891232</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=294392417</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=304588805</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>나에게 고맙다</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>30만 부 기념 전면개정판</t>
-        </is>
-      </c>
+          <t>잘될 수밖에 없는 너에게</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>전승환 (지은이)</t>
+          <t>최서영 (지은이)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5469,37 +5469,33 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>19000</v>
+        <v>19500</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>9791191891072</t>
+          <t>9791191891201</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=289269041</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=299808248</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>럭키 LUCKY</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>내 안에 잠든 운을 깨우는 7가지 법칙</t>
-        </is>
-      </c>
+          <t>나로서 충분히 괜찮은 사람</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>김도윤 (지은이)</t>
+          <t>김재식 (지은이)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5509,42 +5505,42 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>자기계발</t>
+          <t>에세이</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
+          <t>2022-05-10</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>9791191891027</t>
+          <t>9791191891096</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=278177114</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=294392417</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>그렇다면 나를 응원할 수밖에 (윈터 에디션)</t>
+          <t>나에게 고맙다</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>멋대로지만 제대로 사는 중입니다</t>
+          <t>30만 부 기념 전면개정판</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>김수민 (지은이)</t>
+          <t>전승환 (지은이)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5559,33 +5555,37 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>15000</v>
+        <v>19000</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>9791197037191</t>
+          <t>9791191891072</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=283440909</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=289269041</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>작은 별이지만 빛나고 있어 (30만부 기념 미드나잇 에디션)</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>럭키 LUCKY</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>내 안에 잠든 운을 깨우는 7가지 법칙</t>
+        </is>
+      </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>소윤 (지은이)</t>
+          <t>김도윤 (지은이)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5595,38 +5595,42 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>에세이</t>
+          <t>자기계발</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-08-25</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>9791197037153</t>
+          <t>9791191891027</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=367659804</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=278177114</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>좋은 건 같이 봐요</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr"/>
+          <t>그렇다면 나를 응원할 수밖에 (윈터 에디션)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>멋대로지만 제대로 사는 중입니다</t>
+        </is>
+      </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>엄지사진관 (지은이)</t>
+          <t>김수민 (지은이)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5641,7 +5645,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2021-01-27</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -5649,25 +5653,25 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>9791197037146</t>
+          <t>9791197037191</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=262375795</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=283440909</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>안녕, 소중한 사람</t>
+          <t>작은 별이지만 빛나고 있어 (30만부 기념 미드나잇 에디션)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>정한경 (지은이)</t>
+          <t>소윤 (지은이)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5682,7 +5686,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -5690,55 +5694,137 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>9791197037122</t>
+          <t>9791197037153</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=251524184</t>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=367659804</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
+          <t>좋은 건 같이 봐요</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>엄지사진관 (지은이)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>북로망스</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>에세이</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2021-01-27</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>9791197037146</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=262375795</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>안녕, 소중한 사람</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>정한경 (지은이)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>북로망스</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>에세이</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>19000</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>9791197037122</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=251524184</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
           <t>나는 나를 사랑한다</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>나를 잃지 않고 타인을 사랑하기 위하여</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>이숙명 (지은이)</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>북로망스</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>에세이</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>2020-06-24</t>
         </is>
       </c>
-      <c r="G122" t="n">
+      <c r="G124" t="n">
         <v>14800</v>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>9791197037108</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="I124" t="inlineStr">
         <is>
           <t>https://www.aladin.co.kr/shop/wproduct.aspx?ItemId=242494208</t>
         </is>
@@ -5755,7 +5841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5855,37 +5941,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A Briefing on Knowledge for Conversations Worth Having (Special Limited Edition)</t>
+          <t>Everything Has Its Owner</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The knowledge behind thoughtful, well-informed conversation.</t>
+          <t>The first novel from a book creator whose words have reached tens of thousands of readers.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>품격 있는 대화를 위한 지식 브리핑 (10만 부 기념 특별 한정판)</t>
+          <t>물각유주</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>김진</t>
+          <t>공백</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9791124038413</t>
+          <t>9791124038871</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5897,37 +5983,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Money Trend 2027</t>
+          <t>A Briefing on Knowledge for Conversations Worth Having (Special Limited Edition)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>55 currents of money that turn upheaval into opportunity.</t>
+          <t>The knowledge behind thoughtful, well-informed conversation.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>머니 트렌드 2027</t>
+          <t>품격 있는 대화를 위한 지식 브리핑 (10만 부 기념 특별 한정판)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>정태익, 김도윤, 김광석, 김용섭, 김학렬, 박세익, 박정호, 이효석</t>
+          <t>김진</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9791124038826</t>
+          <t>9791124038413</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5939,27 +6025,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Meeting Philosophy for the First Time</t>
+          <t>Money Trend 2027</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The moment philosophy walks into your life.</t>
+          <t>55 currents of money that turn upheaval into opportunity.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>처음 만나는 철학의 세계</t>
+          <t>머니 트렌드 2027</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>성창원</t>
+          <t>정태익, 김도윤, 김광석, 김용섭, 김학렬, 박세익, 박정호, 이효석</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5969,7 +6055,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9791124038833</t>
+          <t>9791124038826</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5981,37 +6067,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>How Smart People Talk</t>
+          <t>Meeting Philosophy for the First Time</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Speaking strategies of people who earn trust without talking long.</t>
+          <t>The moment philosophy walks into your life.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>똑똑한 사람은 어떻게 말하는가</t>
+          <t>처음 만나는 철학의 세계</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>이시한</t>
+          <t>성창원</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9791124038642</t>
+          <t>9791124038833</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -6023,37 +6109,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>The Texture of Memory</t>
+          <t>How Smart People Talk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unable to recognize faces, she reads people through cloth and gait.</t>
+          <t>Speaking strategies of people who earn trust without talking long.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>기억의 무늬</t>
+          <t>똑똑한 사람은 어떻게 말하는가</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>백희성</t>
+          <t>이시한</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>9791124038604</t>
+          <t>9791124038642</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -6065,37 +6151,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Your Happiness Is My Joy</t>
+          <t>The Texture of Memory</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>To love someone is to find your joy in theirs.</t>
+          <t>Unable to recognize faces, she reads people through cloth and gait.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>너의 행복은 나의 기쁨이야</t>
+          <t>기억의 무늬</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>정한경</t>
+          <t>백희성</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9791124038574</t>
+          <t>9791124038604</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -6107,37 +6193,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>The Secret of Magnetic People</t>
+          <t>Your Happiness Is My Joy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Graceful words and bearing that move hearts.</t>
+          <t>To love someone is to find your joy in theirs.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>끌리는 사람의 비밀</t>
+          <t>너의 행복은 나의 기쁨이야</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>조수빈</t>
+          <t>정한경</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9791124038567</t>
+          <t>9791124038574</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -6149,37 +6235,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>The Double-Decker Bus of Richmond Hill</t>
+          <t>The Secret of Magnetic People</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>If you could change the past, would you choose differently?</t>
+          <t>Graceful words and bearing that move hearts.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>리치먼드힐의 이층 버스</t>
+          <t>끌리는 사람의 비밀</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>이경진</t>
+          <t>조수빈</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9791124038499</t>
+          <t>9791124038567</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -6191,37 +6277,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>The Original Code</t>
+          <t>The Double-Decker Bus of Richmond Hill</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Work like yourself, succeed like yourself.</t>
+          <t>If you could change the past, would you choose differently?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>오리지널 코드</t>
+          <t>리치먼드힐의 이층 버스</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>오은환</t>
+          <t>이경진</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9791124038369</t>
+          <t>9791124038499</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -6233,37 +6319,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>My Perfect Funeral</t>
+          <t>The Original Code</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Warm hope, found between life and death.</t>
+          <t>Work like yourself, succeed like yourself.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>나의 완벽한 장례식</t>
+          <t>오리지널 코드</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>조현선</t>
+          <t>오은환</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9791124038192</t>
+          <t>9791124038369</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -6275,37 +6361,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Callie's Routine English</t>
+          <t>My Perfect Funeral</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10 minutes a day, 90 days, one lasting English habit.</t>
+          <t>Warm hope, found between life and death.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>캘리쌤의 루틴 잉글리시</t>
+          <t>나의 완벽한 장례식</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>캘리쌤</t>
+          <t>조현선</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9791124038123</t>
+          <t>9791124038192</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -6317,37 +6403,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mileage Hours</t>
+          <t>Callie's Routine English</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The art of designing a life of greater quality.</t>
+          <t>10 minutes a day, 90 days, one lasting English habit.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>마일리지 아워</t>
+          <t>캘리쌤의 루틴 잉글리시</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>최유나</t>
+          <t>캘리쌤</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9791124038093</t>
+          <t>9791124038123</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -6359,37 +6445,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>The Dignity of Adulthood</t>
+          <t>Mileage Hours</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The life attitudes that make a real grown-up.</t>
+          <t>The art of designing a life of greater quality.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>어른의 품위</t>
+          <t>마일리지 아워</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>최서영</t>
+          <t>최유나</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9791193937693</t>
+          <t>9791124038093</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -6401,37 +6487,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Money Trend 2026</t>
+          <t>The Dignity of Adulthood</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50 survival formulas for the flow of money in uncertain times.</t>
+          <t>The life attitudes that make a real grown-up.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>머니 트렌드 2026</t>
+          <t>어른의 품위</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>김도윤, 정태익, 김광석, 김승주, 김용섭, 김학렬(빠숑), 김현준, 최재붕</t>
+          <t>최서영</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9791193937686</t>
+          <t>9791193937693</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -6443,37 +6529,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Meeting the Quantum World for the First Time</t>
+          <t>Money Trend 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>From quantum mechanics to quantum computers.</t>
+          <t>50 survival formulas for the flow of money in uncertain times.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>처음 만나는 양자의 세계</t>
+          <t>머니 트렌드 2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>채은미</t>
+          <t>김도윤, 정태익, 김광석, 김승주, 김용섭, 김학렬(빠숑), 김현준, 최재붕</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>9791193937990</t>
+          <t>9791193937686</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -6485,22 +6571,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Knowledge Beyond the Gaze</t>
+          <t>Meeting the Quantum World for the First Time</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nine questions that reveal hidden worlds.</t>
+          <t>From quantum mechanics to quantum computers.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>시선 너머의 지식</t>
+          <t>처음 만나는 양자의 세계</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>윤수용</t>
+          <t>채은미</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -6510,12 +6596,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>9791193937785</t>
+          <t>9791193937990</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6527,37 +6613,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>The Marigold Atelier Collection (Limited Edition Box Set)</t>
+          <t>Knowledge Beyond the Gaze</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The complete, internationally acclaimed Marigold trilogy in one set.</t>
+          <t>Nine questions that reveal hidden worlds.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>메리골드 아틀리에 컬렉션 특별 한정판 세트</t>
+          <t>시선 너머의 지식</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>윤정은</t>
+          <t>윤수용</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9791193937754</t>
+          <t>9791193937785</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6569,17 +6655,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marigold Mind Garden (Atelier Collection)</t>
+          <t>The Marigold Atelier Collection (Limited Edition Box Set)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What if unhealed wounds could bloom into flowers and trees?</t>
+          <t>The complete, internationally acclaimed Marigold trilogy in one set.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>메리골드 마음 식물원 (아틀리에 컬렉션)</t>
+          <t>메리골드 아틀리에 컬렉션 특별 한정판 세트</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6599,7 +6685,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>9791193937723</t>
+          <t>9791193937754</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6611,17 +6697,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marigold Mind Photo Studio (Atelier Collection)</t>
+          <t>Marigold Mind Garden (Atelier Collection)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The second Marigold story, more delicate and thoughtful than the first.</t>
+          <t>What if unhealed wounds could bloom into flowers and trees?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>메리골드 마음 사진관 (아틀리에 컬렉션)</t>
+          <t>메리골드 마음 식물원 (아틀리에 컬렉션)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6641,7 +6727,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>9791193937730</t>
+          <t>9791193937723</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6653,17 +6739,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marigold Mind Laundry (Atelier Collection)</t>
+          <t>Marigold Mind Photo Studio (Atelier Collection)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A beloved K-healing fantasy returns in a special edition.</t>
+          <t>The second Marigold story, more delicate and thoughtful than the first.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>메리골드 마음 세탁소 (아틀리에 컬렉션)</t>
+          <t>메리골드 마음 사진관 (아틀리에 컬렉션)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6683,7 +6769,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>9791193937310</t>
+          <t>9791193937730</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6695,37 +6781,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Meet Me in Our Paradise</t>
+          <t>Marigold Mind Laundry (Atelier Collection)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>For you, crossing this season together with me.</t>
+          <t>A beloved K-healing fantasy returns in a special edition.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>우리의 낙원에서 만나자</t>
+          <t>메리골드 마음 세탁소 (아틀리에 컬렉션)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>하태완</t>
+          <t>윤정은</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>9791193937655</t>
+          <t>9791193937310</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6737,37 +6823,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Core Thinking</t>
+          <t>Meet Me in Our Paradise</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The art of thinking that cuts to the essence of work.</t>
+          <t>For you, crossing this season together with me.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>코어 씽킹 Core Thinking</t>
+          <t>우리의 낙원에서 만나자</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>김범섭</t>
+          <t>하태완</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>9791193937624</t>
+          <t>9791193937655</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6779,37 +6865,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>You Are Always Okay</t>
+          <t>Core Thinking</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>How to steady yourself and stand firm after a shaky time.</t>
+          <t>The art of thinking that cuts to the essence of work.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>당신은 언제나 괜찮다</t>
+          <t>코어 씽킹 Core Thinking</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>이현수</t>
+          <t>김범섭</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>9791193937617</t>
+          <t>9791193937624</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -6821,37 +6907,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Everything Will Be Alright, Until Happiness Overflows</t>
+          <t>You Are Always Okay</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gentle words for the feelings we never managed to say out loud.</t>
+          <t>How to steady yourself and stand firm after a shaky time.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>다 좋아질 거야, 행복이 쏟아질 만큼</t>
+          <t>당신은 언제나 괜찮다</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>길연우</t>
+          <t>이현수</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>9791193937594</t>
+          <t>9791193937617</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -6863,37 +6949,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Time to Write Myself</t>
+          <t>Everything Will Be Alright, Until Happiness Overflows</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>One line a day can change a life.</t>
+          <t>Gentle words for the feelings we never managed to say out loud.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>나를 쓰는 시간</t>
+          <t>다 좋아질 거야, 행복이 쏟아질 만큼</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>장예원</t>
+          <t>길연우</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>9791193937365</t>
+          <t>9791193937594</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -6905,37 +6991,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Every Step Has Its Reason</t>
+          <t>Time to Write Myself</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A former TV reporter's journey toward happiness, offered as a map.</t>
+          <t>One line a day can change a life.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>모든 걸음에는 이유가 있다</t>
+          <t>나를 쓰는 시간</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>김아영</t>
+          <t>장예원</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>9791193937563</t>
+          <t>9791193937365</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -6947,37 +7033,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>The AI Supremacy War: ChatGPT, DeepSeek, and What Comes Next</t>
+          <t>Every Step Has Its Reason</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Make the AI era your weapon instead of falling behind.</t>
+          <t>A former TV reporter's journey toward happiness, offered as a map.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AI 패권 전쟁</t>
+          <t>모든 걸음에는 이유가 있다</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>이시한</t>
+          <t>김아영</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>9791193937549</t>
+          <t>9791193937563</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -6989,37 +7075,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>When You Don't Know What You Want</t>
+          <t>The AI Supremacy War: ChatGPT, DeepSeek, and What Comes Next</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>150 lines from literature and philosophy to find your way again.</t>
+          <t>Make the AI era your weapon instead of falling behind.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>내가 원하는 것을 나도 모를 때</t>
+          <t>AI 패권 전쟁</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>전승환</t>
+          <t>이시한</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>9791193937150</t>
+          <t>9791193937549</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -7031,22 +7117,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Attitude Toward Life: Moving Forward Without Wavering</t>
+          <t>When You Don't Know What You Want</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Can people really change, and what changes them?</t>
+          <t>150 lines from literature and philosophy to find your way again.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>삶의 태도</t>
+          <t>내가 원하는 것을 나도 모를 때</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>반건호</t>
+          <t>전승환</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -7056,12 +7142,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>9791193937402</t>
+          <t>9791193937150</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -7073,37 +7159,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>The Things That Set a Life Free</t>
+          <t>Attitude Toward Life: Moving Forward Without Wavering</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Putting the happiness that makes your heart race first.</t>
+          <t>Can people really change, and what changes them?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>인생을 자유롭게 하는 것들</t>
+          <t>삶의 태도</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>나용민, 유숙현</t>
+          <t>반건호</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>9791193937389</t>
+          <t>9791193937402</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -7115,37 +7201,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>British Dad Peter's 3-Minute Daily English Conversations (Spring-Bound Daily Calendar)</t>
+          <t>The Things That Set a Life Free</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A flip calendar that gets parents and kids talking in English daily.</t>
+          <t>Putting the happiness that makes your heart race first.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>영국 아빠 피터의 하루 3분 영어 대화 (스프링)</t>
+          <t>인생을 자유롭게 하는 것들</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>피터 빈트</t>
+          <t>나용민, 유숙현</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Parenting</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>9791193937280</t>
+          <t>9791193937389</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -7157,37 +7243,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Money Trend 2025</t>
+          <t>British Dad Peter's 3-Minute Daily English Conversations (Spring-Bound Daily Calendar)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>55 scenarios for seizing the next opportunities in wealth.</t>
+          <t>A flip calendar that gets parents and kids talking in English daily.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>머니 트렌드 2025</t>
+          <t>영국 아빠 피터의 하루 3분 영어 대화 (스프링)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>정태익, 김도윤, 김광석, 김용섭, 김현준, 정수종, 채상욱, 최재붕</t>
+          <t>피터 빈트</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Parenting</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>9791193937211</t>
+          <t>9791193937280</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -7199,37 +7285,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>How Emotionally Rich Children Grow</t>
+          <t>Money Trend 2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>An emotion-centered approach to raising children who know how to be happy.</t>
+          <t>55 scenarios for seizing the next opportunities in wealth.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>마음이 부자인 아이는 어떻게 성장하는가</t>
+          <t>머니 트렌드 2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>박소영</t>
+          <t>정태익, 김도윤, 김광석, 김용섭, 김현준, 정수종, 채상욱, 최재붕</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Parenting</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>9791193937228</t>
+          <t>9791193937211</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -7241,37 +7327,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>The Night I Asked After Mom</t>
+          <t>How Emotionally Rich Children Grow</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The one person in the world who is always on your side.</t>
+          <t>An emotion-centered approach to raising children who know how to be happy.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>엄마에게 안부를 묻는 밤</t>
+          <t>마음이 부자인 아이는 어떻게 성장하는가</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>박애희</t>
+          <t>박소영</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Parenting</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>9791193937242</t>
+          <t>9791193937228</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -7283,37 +7369,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Where the Light Leads</t>
+          <t>The Night I Asked After Mom</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A Paris architect is offered a historic mansion and learns why.</t>
+          <t>The one person in the world who is always on your side.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>빛이 이끄는 곳으로</t>
+          <t>엄마에게 안부를 묻는 밤</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>백희성</t>
+          <t>박애희</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9791193937198</t>
+          <t>9791193937242</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -7325,37 +7411,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>The Art of Likability (Twinkle Edition)</t>
+          <t>Where the Light Leads</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The principles of charm that make relationships, work, and life flow.</t>
+          <t>A Paris architect is offered a historic mansion and learns why.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>호감의 시작 (트윙클 에디션)</t>
+          <t>빛이 이끄는 곳으로</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>희렌최</t>
+          <t>백희성</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>9791193937143</t>
+          <t>9791193937198</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -7367,37 +7453,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Even So, I Liked Myself</t>
+          <t>The Art of Likability (Twinkle Edition)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>From a million-subscriber peak to rock bottom, and unexpectedly happier.</t>
+          <t>The principles of charm that make relationships, work, and life flow.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>그럼에도 불구하고 나는 내가 좋았어</t>
+          <t>호감의 시작 (트윙클 에디션)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>박채린</t>
+          <t>희렌최</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>9791193937105</t>
+          <t>9791193937143</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -7409,37 +7495,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>How Smart Kids Think and Ask Questions</t>
+          <t>Even So, I Liked Myself</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Survival strategies for self-driven children in an age of fading thinking skills.</t>
+          <t>From a million-subscriber peak to rock bottom, and unexpectedly happier.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>똑똑한 아이는 어떻게 생각하고 질문하는가</t>
+          <t>그럼에도 불구하고 나는 내가 좋았어</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>이시한</t>
+          <t>박채린</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Parenting</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>9791193937037</t>
+          <t>9791193937105</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -7451,37 +7537,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>The Lovable Egoist</t>
+          <t>How Smart Kids Think and Ask Questions</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The art of protecting yourself and still being loved.</t>
+          <t>Survival strategies for self-driven children in an age of fading thinking skills.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>사랑받는 이기주의자</t>
+          <t>똑똑한 아이는 어떻게 생각하고 질문하는가</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>박코</t>
+          <t>이시한</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Parenting</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>9791193937051</t>
+          <t>9791193937037</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -7493,37 +7579,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>What I Learned from a Thousand Lives</t>
+          <t>The Lovable Egoist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>On what matters more than money, fame, or time.</t>
+          <t>The art of protecting yourself and still being loved.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>내가 천 개의 인생에서 배운 것들</t>
+          <t>사랑받는 이기주의자</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>김도윤</t>
+          <t>박코</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>9791198530394</t>
+          <t>9791193937051</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -7535,37 +7621,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>The Positive-Sum Person</t>
+          <t>What I Learned from a Thousand Lives</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A psychology of inner change that raises the quality of your life.</t>
+          <t>On what matters more than money, fame, or time.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>양수인간</t>
+          <t>내가 천 개의 인생에서 배운 것들</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>최설민</t>
+          <t>김도윤</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>9791193937006</t>
+          <t>9791198530394</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -7577,37 +7663,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>An Elder's Dream, Vol. 1</t>
+          <t>The Positive-Sum Person</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A story for all of us walking toward twilight.</t>
+          <t>A psychology of inner change that raises the quality of your life.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>노인의 꿈 : 첫 번째 이야기</t>
+          <t>양수인간</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>백원달</t>
+          <t>최설민</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>9791191891478</t>
+          <t>9791193937006</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7619,7 +7705,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>An Elder's Dream, Vol. 2</t>
+          <t>An Elder's Dream, Vol. 1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7629,7 +7715,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>노인의 꿈 : 두 번째 이야기</t>
+          <t>노인의 꿈 : 첫 번째 이야기</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7649,7 +7735,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>9791191891485</t>
+          <t>9791191891478</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7661,37 +7747,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>How Smart People Think and Ask Questions</t>
+          <t>An Elder's Dream, Vol. 2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Survival strategies for staying ahead as thinking skills fade.</t>
+          <t>A story for all of us walking toward twilight.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>똑똑한 사람은 어떻게 생각하고 질문하는가</t>
+          <t>노인의 꿈 : 두 번째 이야기</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>이시한</t>
+          <t>백원달</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>9791191891492</t>
+          <t>9791191891485</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7703,37 +7789,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Take It Easy, Like a Walk (Green Edition)</t>
+          <t>How Smart People Think and Ask Questions</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Words for anyone trying to find some breathing room in life.</t>
+          <t>Survival strategies for staying ahead as thinking skills fade.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>산책하듯 가볍게 (풀빛 에디션)</t>
+          <t>똑똑한 사람은 어떻게 생각하고 질문하는가</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>정우성</t>
+          <t>이시한</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>9791191891447</t>
+          <t>9791191891492</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7745,22 +7831,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>May Everything You Do Go Well</t>
+          <t>Take It Easy, Like a Walk (Green Edition)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wherever you are, whatever you do, hope is with you.</t>
+          <t>Words for anyone trying to find some breathing room in life.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>하는 일마다 잘되리라</t>
+          <t>산책하듯 가볍게 (풀빛 에디션)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>전승환</t>
+          <t>정우성</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -7770,12 +7856,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>9791198530301</t>
+          <t>9791191891447</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7787,37 +7873,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Money Trend 2024</t>
+          <t>May Everything You Do Go Well</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>57 keywords that map the flow of money in Korea.</t>
+          <t>Wherever you are, whatever you do, hope is with you.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>머니 트렌드 2024</t>
+          <t>하는 일마다 잘되리라</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>김도윤, 정태익, 김용섭, 김현준, 전영수, 채상욱, 최재붕, 홍춘욱</t>
+          <t>전승환</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>9791191891416</t>
+          <t>9791198530301</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7829,37 +7915,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Everyone Blooms</t>
+          <t>Money Trend 2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>A self-belief essay for living every day with more anticipation.</t>
+          <t>57 keywords that map the flow of money in Korea.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>꽃은 누구에게나 핀다</t>
+          <t>머니 트렌드 2024</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>오은환</t>
+          <t>김도윤, 정태익, 김용섭, 김현준, 전영수, 채상욱, 최재붕, 홍춘욱</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>9791191891409</t>
+          <t>9791191891416</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7871,22 +7957,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>I Like Playing with You Best</t>
+          <t>Everyone Blooms</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>For the one you cherish, thank and love.</t>
+          <t>A self-belief essay for living every day with more anticipation.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>나는 너랑 노는 게 제일 좋아</t>
+          <t>꽃은 누구에게나 핀다</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>하태완</t>
+          <t>오은환</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -7896,12 +7982,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>9791191891362</t>
+          <t>9791191891409</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7913,22 +7999,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Freedom of Mind</t>
+          <t>I Like Playing with You Best</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Happiness is a mind that is not bound to anything.</t>
+          <t>For the one you cherish, thank and love.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>마음의 자유</t>
+          <t>나는 너랑 노는 게 제일 좋아</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>정윤</t>
+          <t>하태완</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -7938,12 +8024,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>9791191891355</t>
+          <t>9791191891362</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7955,22 +8041,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>It's Okay to Be Dented</t>
+          <t>Freedom of Mind</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Words from a duck who is already dented.</t>
+          <t>Happiness is a mind that is not bound to anything.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>찌그러져도 괜찮아</t>
+          <t>마음의 자유</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>찌오(임임)</t>
+          <t>정윤</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -7980,12 +8066,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>9791191891324</t>
+          <t>9791191891355</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -7997,27 +8083,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>If You Ask What I Regret Most in Life</t>
+          <t>It's Okay to Be Dented</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>"If you could go back, what would you change?"</t>
+          <t>Words from a duck who is already dented.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>인생에서 가장 후회되는 게 뭐냐고 묻는다면</t>
+          <t>찌그러져도 괜찮아</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>노우티</t>
+          <t>찌오(임임)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Humanities</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -8027,7 +8113,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>9791191891331</t>
+          <t>9791191891324</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8039,37 +8125,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>If We Fight in the Morning, I'll Kiss You at Night</t>
+          <t>If You Ask What I Regret Most in Life</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Every feeling of love, caught in words and photographs.</t>
+          <t>"If you could go back, what would you change?"</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>당신과 아침에 싸우면 밤에는 입맞출 겁니다</t>
+          <t>인생에서 가장 후회되는 게 뭐냐고 묻는다면</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>유래혁</t>
+          <t>노우티</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Humanities</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>9791191891263</t>
+          <t>9791191891331</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8081,37 +8167,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GPT Generation: How ChatGPT Will Change Humanity's Future</t>
+          <t>If We Fight in the Morning, I'll Kiss You at Night</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A mega-trend is only beginning, and it will reshape everyday life.</t>
+          <t>Every feeling of love, caught in words and photographs.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GPT 제너레이션 : 챗GPT가 바꿀 우리 인류의 미래</t>
+          <t>당신과 아침에 싸우면 밤에는 입맞출 겁니다</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>이시한</t>
+          <t>유래혁</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>9791191891270</t>
+          <t>9791191891263</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8123,37 +8209,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>I'm Odungi, Actually!</t>
+          <t>GPT Generation: How ChatGPT Will Change Humanity's Future</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The happiest duck in the world.</t>
+          <t>A mega-trend is only beginning, and it will reshape everyday life.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>오둥이입니다만!</t>
+          <t>GPT 제너레이션 : 챗GPT가 바꿀 우리 인류의 미래</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>송 스튜디오</t>
+          <t>이시한</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>9791191891256</t>
+          <t>9791191891270</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8165,22 +8251,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>I'll Pour Happiness In for You</t>
+          <t>I'm Odungi, Actually!</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gem-like stories to carry your ordinary life to its brightest moments.</t>
+          <t>The happiest duck in the world.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>행복을 담아줄게</t>
+          <t>오둥이입니다만!</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>나란</t>
+          <t>송 스튜디오</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -8190,12 +8276,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>9791191891249</t>
+          <t>9791191891256</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8207,22 +8293,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>I Like Who I Am Today</t>
+          <t>I'll Pour Happiness In for You</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The soft, squishy diary of Molang, the positive rabbit.</t>
+          <t>Gem-like stories to carry your ordinary life to its brightest moments.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>나는 오늘의 내가 좋아</t>
+          <t>행복을 담아줄게</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>윤혜지(하얀오리)</t>
+          <t>나란</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -8232,12 +8318,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2023-01-30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>9791191891126</t>
+          <t>9791191891249</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8249,37 +8335,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Money Trend 2023</t>
+          <t>I Like Who I Am Today</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>45 keywords that map the flow of money in Korea.</t>
+          <t>The soft, squishy diary of Molang, the positive rabbit.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>머니 트렌드 2023</t>
+          <t>나는 오늘의 내가 좋아</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>부동산읽어주는남자(정태익), 김도윤, 김경민, 김상균, 전영수, 최준철, 홍춘욱</t>
+          <t>윤혜지(하얀오리)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>9791191891232</t>
+          <t>9791191891126</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8291,37 +8377,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>You're Bound to Do Well</t>
+          <t>Money Trend 2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Practical encouragement for living and working better.</t>
+          <t>45 keywords that map the flow of money in Korea.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>잘될 수밖에 없는 너에게</t>
+          <t>머니 트렌드 2023</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>최서영</t>
+          <t>부동산읽어주는남자(정태익), 김도윤, 김경민, 김상균, 전영수, 최준철, 홍춘욱</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>9791191891201</t>
+          <t>9791191891232</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8333,22 +8419,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Good Enough, Just as I Am</t>
+          <t>You're Bound to Do Well</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>A letter of warm empathy and encouragement.</t>
+          <t>Practical encouragement for living and working better.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>나로서 충분히 괜찮은 사람</t>
+          <t>잘될 수밖에 없는 너에게</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>김재식</t>
+          <t>최서영</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -8358,12 +8444,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>9791191891096</t>
+          <t>9791191891201</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8375,22 +8461,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Thank You, Me (Fully Revised Edition)</t>
+          <t>Good Enough, Just as I Am</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A healing essay collection, fully revised to mark 300,000 copies sold.</t>
+          <t>A letter of warm empathy and encouragement.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>나에게 고맙다</t>
+          <t>나로서 충분히 괜찮은 사람</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>전승환</t>
+          <t>김재식</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -8400,12 +8486,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>2022-05-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>9791191891072</t>
+          <t>9791191891096</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8417,37 +8503,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LUCKY: 7 Rules for Awakening the Luck Within</t>
+          <t>Thank You, Me (Fully Revised Edition)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>What 1,000 successful people all said: "I was lucky."</t>
+          <t>A healing essay collection, fully revised to mark 300,000 copies sold.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>럭키 LUCKY</t>
+          <t>나에게 고맙다</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>김도윤</t>
+          <t>전승환</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Self-Help</t>
+          <t>Essay</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>9791191891027</t>
+          <t>9791191891072</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -8459,37 +8545,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Then I Have No Choice but to Cheer Myself On (Winter Edition)</t>
+          <t>LUCKY: 7 Rules for Awakening the Luck Within</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Doing life my own way, and doing it right.</t>
+          <t>What 1,000 successful people all said: "I was lucky."</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>그렇다면 나를 응원할 수밖에 (윈터 에디션)</t>
+          <t>럭키 LUCKY</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>김수민</t>
+          <t>김도윤</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Essay</t>
+          <t>Self-Help</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
+          <t>2021-08-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>9791197037191</t>
+          <t>9791191891027</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -8501,22 +8587,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A Small Star, Still Shining (Midnight Edition)</t>
+          <t>Then I Have No Choice but to Cheer Myself On (Winter Edition)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A small, steady encouragement for everyone enduring the day.</t>
+          <t>Doing life my own way, and doing it right.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>작은 별이지만 빛나고 있어 (30만부 기념 미드나잇 에디션)</t>
+          <t>그렇다면 나를 응원할 수밖에 (윈터 에디션)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>소윤</t>
+          <t>김수민</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -8526,12 +8612,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>9791197037153</t>
+          <t>9791197037191</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8543,22 +8629,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Let's Look at the Good Things Together</t>
+          <t>A Small Star, Still Shining (Midnight Edition)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The best things I've seen, offered to you.</t>
+          <t>A small, steady encouragement for everyone enduring the day.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>좋은 건 같이 봐요</t>
+          <t>작은 별이지만 빛나고 있어 (30만부 기념 미드나잇 에디션)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>엄지사진관</t>
+          <t>소윤</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -8568,12 +8654,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2021-01-27</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>9791197037146</t>
+          <t>9791197037153</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8585,22 +8671,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Hello, Precious One</t>
+          <t>Let's Look at the Good Things Together</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Everything about the preciousness you should hold on to.</t>
+          <t>The best things I've seen, offered to you.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>안녕, 소중한 사람</t>
+          <t>좋은 건 같이 봐요</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>정한경</t>
+          <t>엄지사진관</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8610,12 +8696,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2021-01-27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>9791197037122</t>
+          <t>9791197037146</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8627,40 +8713,82 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>Hello, Precious One</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Everything about the preciousness you should hold on to.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>안녕, 소중한 사람</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>정한경</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Essay</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>9791197037122</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>rights@thebookman.co.kr</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>I Love Myself</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>How to love others without losing yourself.</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>나는 나를 사랑한다</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>이숙명</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Essay</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>2020-06-24</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>9791197037108</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>rights@thebookman.co.kr</t>
         </is>
